--- a/AIRCRAFT_AIRFOIL_TRANSFORM_MICRO26.xlsx
+++ b/AIRCRAFT_AIRFOIL_TRANSFORM_MICRO26.xlsx
@@ -21,6 +21,40 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <authors>
+    <author>Unknown Author</author>
+  </authors>
+  <commentList>
+    <comment ref="C15" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">b_semi is an ABSOLUTE input in skeleton_equations_micro.txt (main lifting-panel semi-span, 518 mm). It is deliberately NOT b/2: b/2 = 575 = 518 panel + 57 mm vertical winglet tip, modelled downstream. Formula "=C5/2" replaced with the literal. Source: user, skeleton_equations_micro.txt.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C16" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Was "=(C6+C7)*C15", which equals S_w only while C15 = b/2. C15 is now the absolutised 518, so this uses the canonical definition S_w = (c_root + c_tip)/2 * b to stay consistent with skeleton_equations_micro.txt.</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="114">
   <si>
@@ -378,7 +412,7 @@
     <numFmt numFmtId="168" formatCode="0.00"/>
     <numFmt numFmtId="169" formatCode="0.00000"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="14">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -447,6 +481,11 @@
       <name val="Segoe UI"/>
       <family val="0"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b val="true"/>
@@ -631,15 +670,15 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -651,7 +690,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -982,7 +1021,7 @@
         <v>9</v>
       </c>
       <c r="C5" s="7" t="n">
-        <v>1100</v>
+        <v>1150</v>
       </c>
       <c r="D5" s="6" t="s">
         <v>10</v>
@@ -1002,7 +1041,7 @@
         <v>14</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>300</v>
+        <v>225</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>10</v>
@@ -1022,7 +1061,7 @@
         <v>18</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>180</v>
+        <v>225</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>10</v>
@@ -1042,7 +1081,7 @@
         <v>22</v>
       </c>
       <c r="C8" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>23</v>
@@ -1062,7 +1101,7 @@
         <v>27</v>
       </c>
       <c r="C9" s="8" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>23</v>
@@ -1082,7 +1121,7 @@
         <v>31</v>
       </c>
       <c r="C10" s="8" t="n">
-        <v>0</v>
+        <v>11.02</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>23</v>
@@ -1152,8 +1191,7 @@
         <v>45</v>
       </c>
       <c r="C15" s="9" t="n">
-        <f aca="false">C5/2</f>
-        <v>550</v>
+        <v>518</v>
       </c>
       <c r="D15" s="6" t="s">
         <v>10</v>
@@ -1173,8 +1211,8 @@
         <v>49</v>
       </c>
       <c r="C16" s="10" t="n">
-        <f aca="false">(C6+C7)*C15</f>
-        <v>264000</v>
+        <f aca="false">(C6+C7)/2*C5</f>
+        <v>258750</v>
       </c>
       <c r="D16" s="6" t="s">
         <v>50</v>
@@ -1195,7 +1233,7 @@
       </c>
       <c r="C17" s="10" t="n">
         <f aca="false">C16/10000</f>
-        <v>26.4</v>
+        <v>25.875</v>
       </c>
       <c r="D17" s="6" t="s">
         <v>55</v>
@@ -1216,7 +1254,7 @@
       </c>
       <c r="C18" s="11" t="n">
         <f aca="false">C5^2/C16</f>
-        <v>4.58333333333333</v>
+        <v>5.11111111111111</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>60</v>
@@ -1237,7 +1275,7 @@
       </c>
       <c r="C19" s="11" t="n">
         <f aca="false">C7/C6</f>
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="D19" s="6" t="s">
         <v>60</v>
@@ -1258,7 +1296,7 @@
       </c>
       <c r="C20" s="10" t="n">
         <f aca="false">(2/3)*C6*(1+C19+C19^2)/(1+C19)</f>
-        <v>245</v>
+        <v>225</v>
       </c>
       <c r="D20" s="6" t="s">
         <v>10</v>
@@ -1279,7 +1317,7 @@
       </c>
       <c r="C21" s="10" t="n">
         <f aca="false">(C5/6)*(1+2*C19)/(1+C19)</f>
-        <v>252.083333333333</v>
+        <v>287.5</v>
       </c>
       <c r="D21" s="6" t="s">
         <v>10</v>
@@ -1300,7 +1338,7 @@
       </c>
       <c r="C22" s="9" t="n">
         <f aca="false">C8</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D22" s="6" t="s">
         <v>23</v>
@@ -1460,6 +1498,7 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -1496,18 +1535,18 @@
       </c>
       <c r="E1" s="16" t="n">
         <f aca="false">Control_Panel!$C$6</f>
-        <v>300</v>
+        <v>225</v>
       </c>
       <c r="F1" s="17" t="n">
         <f aca="false">Control_Panel!$C$22</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G1" s="16" t="n">
         <v>0</v>
       </c>
       <c r="H1" s="17" t="n">
         <f aca="false">Control_Panel!$C$10</f>
-        <v>0</v>
+        <v>11.02</v>
       </c>
       <c r="I1" s="17" t="n">
         <f aca="false">Control_Panel!$C$11</f>
@@ -1556,11 +1595,11 @@
       </c>
       <c r="D3" s="20" t="n">
         <f aca="false">(( -A3 - (-0.25) ) * SIN(RADIANS($F$1)) + (B3 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>-10.4698490107503</v>
+        <v>0</v>
       </c>
       <c r="E3" s="20" t="n">
         <f aca="false">(( -A3 - (-0.25) ) * COS(RADIANS($F$1)) - (B3 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-299.862936079297</v>
+        <v>-225</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1576,11 +1615,11 @@
       </c>
       <c r="D4" s="22" t="n">
         <f aca="false">(( -A4 - (-0.25) ) * SIN(RADIANS($F$1)) + (B4 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>-9.87743858326402</v>
+        <v>0.42525</v>
       </c>
       <c r="E4" s="22" t="n">
         <f aca="false">(( -A4 - (-0.25) ) * COS(RADIANS($F$1)) - (B4 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-299.145173663587</v>
+        <v>-224.4465</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1596,11 +1635,11 @@
       </c>
       <c r="D5" s="20" t="n">
         <f aca="false">(( -A5 - (-0.25) ) * SIN(RADIANS($F$1)) + (B5 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>-8.50161978677057</v>
+        <v>1.404</v>
       </c>
       <c r="E5" s="20" t="n">
         <f aca="false">(( -A5 - (-0.25) ) * COS(RADIANS($F$1)) - (B5 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-297.13996752974</v>
+        <v>-222.9075</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1616,11 +1655,11 @@
       </c>
       <c r="D6" s="22" t="n">
         <f aca="false">(( -A6 - (-0.25) ) * SIN(RADIANS($F$1)) + (B6 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>-6.81642752145338</v>
+        <v>2.5875</v>
       </c>
       <c r="E6" s="22" t="n">
         <f aca="false">(( -A6 - (-0.25) ) * COS(RADIANS($F$1)) - (B6 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-294.097926762605</v>
+        <v>-220.58325</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1636,11 +1675,11 @@
       </c>
       <c r="D7" s="20" t="n">
         <f aca="false">(( -A7 - (-0.25) ) * SIN(RADIANS($F$1)) + (B7 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>-4.90431630689458</v>
+        <v>3.91725</v>
       </c>
       <c r="E7" s="20" t="n">
         <f aca="false">(( -A7 - (-0.25) ) * COS(RADIANS($F$1)) - (B7 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-290.145250618123</v>
+        <v>-217.5705</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1656,11 +1695,11 @@
       </c>
       <c r="D8" s="22" t="n">
         <f aca="false">(( -A8 - (-0.25) ) * SIN(RADIANS($F$1)) + (B8 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>-2.7493529942779</v>
+        <v>5.4045</v>
       </c>
       <c r="E8" s="22" t="n">
         <f aca="false">(( -A8 - (-0.25) ) * COS(RADIANS($F$1)) - (B8 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-285.255479036415</v>
+        <v>-213.849</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1676,11 +1715,11 @@
       </c>
       <c r="D9" s="20" t="n">
         <f aca="false">(( -A9 - (-0.25) ) * SIN(RADIANS($F$1)) + (B9 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>-0.185486413754019</v>
+        <v>7.173</v>
       </c>
       <c r="E9" s="20" t="n">
         <f aca="false">(( -A9 - (-0.25) ) * COS(RADIANS($F$1)) - (B9 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-279.401390537146</v>
+        <v>-209.394</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1696,11 +1735,11 @@
       </c>
       <c r="D10" s="22" t="n">
         <f aca="false">(( -A10 - (-0.25) ) * SIN(RADIANS($F$1)) + (B10 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>2.49168265720163</v>
+        <v>9.00225</v>
       </c>
       <c r="E10" s="22" t="n">
         <f aca="false">(( -A10 - (-0.25) ) * COS(RADIANS($F$1)) - (B10 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-272.623693600463</v>
+        <v>-204.24375</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1716,11 +1755,11 @@
       </c>
       <c r="D11" s="20" t="n">
         <f aca="false">(( -A11 - (-0.25) ) * SIN(RADIANS($F$1)) + (B11 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>5.30052396370376</v>
+        <v>10.908</v>
       </c>
       <c r="E11" s="20" t="n">
         <f aca="false">(( -A11 - (-0.25) ) * COS(RADIANS($F$1)) - (B11 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-264.998075427824</v>
+        <v>-198.4545</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1736,11 +1775,11 @@
       </c>
       <c r="D12" s="22" t="n">
         <f aca="false">(( -A12 - (-0.25) ) * SIN(RADIANS($F$1)) + (B12 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>8.20544014620804</v>
+        <v>12.8655</v>
       </c>
       <c r="E12" s="22" t="n">
         <f aca="false">(( -A12 - (-0.25) ) * COS(RADIANS($F$1)) - (B12 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-256.598338647863</v>
+        <v>-192.0825</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1756,11 +1795,11 @@
       </c>
       <c r="D13" s="20" t="n">
         <f aca="false">(( -A13 - (-0.25) ) * SIN(RADIANS($F$1)) + (B13 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>11.2182811124166</v>
+        <v>14.886</v>
       </c>
       <c r="E13" s="20" t="n">
         <f aca="false">(( -A13 - (-0.25) ) * COS(RADIANS($F$1)) - (B13 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-247.514951927463</v>
+        <v>-185.19525</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1776,11 +1815,11 @@
       </c>
       <c r="D14" s="22" t="n">
         <f aca="false">(( -A14 - (-0.25) ) * SIN(RADIANS($F$1)) + (B14 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>14.3569978134836</v>
+        <v>16.98525</v>
       </c>
       <c r="E14" s="22" t="n">
         <f aca="false">(( -A14 - (-0.25) ) * COS(RADIANS($F$1)) - (B14 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-237.835595158006</v>
+        <v>-177.858</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1796,11 +1835,11 @@
       </c>
       <c r="D15" s="20" t="n">
         <f aca="false">(( -A15 - (-0.25) ) * SIN(RADIANS($F$1)) + (B15 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>17.5975667858286</v>
+        <v>19.1475</v>
       </c>
       <c r="E15" s="20" t="n">
         <f aca="false">(( -A15 - (-0.25) ) * COS(RADIANS($F$1)) - (B15 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-227.646482452011</v>
+        <v>-170.136</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1816,11 +1855,11 @@
       </c>
       <c r="D16" s="22" t="n">
         <f aca="false">(( -A16 - (-0.25) ) * SIN(RADIANS($F$1)) + (B16 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>20.8858781425704</v>
+        <v>21.3345</v>
       </c>
       <c r="E16" s="22" t="n">
         <f aca="false">(( -A16 - (-0.25) ) * COS(RADIANS($F$1)) - (B16 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-217.035779109577</v>
+        <v>-162.09675</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1836,11 +1875,11 @@
       </c>
       <c r="D17" s="20" t="n">
         <f aca="false">(( -A17 - (-0.25) ) * SIN(RADIANS($F$1)) + (B17 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>24.1618256518656</v>
+        <v>23.5035</v>
       </c>
       <c r="E17" s="20" t="n">
         <f aca="false">(( -A17 - (-0.25) ) * COS(RADIANS($F$1)) - (B17 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-206.091441033826</v>
+        <v>-153.80775</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1856,11 +1895,11 @@
       </c>
       <c r="D18" s="22" t="n">
         <f aca="false">(( -A18 - (-0.25) ) * SIN(RADIANS($F$1)) + (B18 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>27.3712994268332</v>
+        <v>25.61625</v>
       </c>
       <c r="E18" s="22" t="n">
         <f aca="false">(( -A18 - (-0.25) ) * COS(RADIANS($F$1)) - (B18 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-194.901633524856</v>
+        <v>-145.3365</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1876,11 +1915,11 @@
       </c>
       <c r="D19" s="20" t="n">
         <f aca="false">(( -A19 - (-0.25) ) * SIN(RADIANS($F$1)) + (B19 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>30.4751804429971</v>
+        <v>27.64575</v>
       </c>
       <c r="E19" s="20" t="n">
         <f aca="false">(( -A19 - (-0.25) ) * COS(RADIANS($F$1)) - (B19 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-183.555045375219</v>
+        <v>-136.7505</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1896,11 +1935,11 @@
       </c>
       <c r="D20" s="22" t="n">
         <f aca="false">(( -A20 - (-0.25) ) * SIN(RADIANS($F$1)) + (B20 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>33.4257739523987</v>
+        <v>29.55825</v>
       </c>
       <c r="E20" s="22" t="n">
         <f aca="false">(( -A20 - (-0.25) ) * COS(RADIANS($F$1)) - (B20 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-172.128058592069</v>
+        <v>-128.10825</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1916,11 +1955,11 @@
       </c>
       <c r="D21" s="20" t="n">
         <f aca="false">(( -A21 - (-0.25) ) * SIN(RADIANS($F$1)) + (B21 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>36.1631831201749</v>
+        <v>31.311</v>
       </c>
       <c r="E21" s="20" t="n">
         <f aca="false">(( -A21 - (-0.25) ) * COS(RADIANS($F$1)) - (B21 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-160.702632733565</v>
+        <v>-119.47275</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1936,11 +1975,11 @@
       </c>
       <c r="D22" s="22" t="n">
         <f aca="false">(( -A22 - (-0.25) ) * SIN(RADIANS($F$1)) + (B22 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>38.6273397982145</v>
+        <v>32.859</v>
       </c>
       <c r="E22" s="22" t="n">
         <f aca="false">(( -A22 - (-0.25) ) * COS(RADIANS($F$1)) - (B22 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-149.279672002385</v>
+        <v>-110.84625</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1956,11 +1995,11 @@
       </c>
       <c r="D23" s="20" t="n">
         <f aca="false">(( -A23 - (-0.25) ) * SIN(RADIANS($F$1)) + (B23 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>40.7462878469721</v>
+        <v>34.14825</v>
       </c>
       <c r="E23" s="20" t="n">
         <f aca="false">(( -A23 - (-0.25) ) * COS(RADIANS($F$1)) - (B23 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-137.856663634767</v>
+        <v>-102.22875</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1976,11 +2015,11 @@
       </c>
       <c r="D24" s="22" t="n">
         <f aca="false">(( -A24 - (-0.25) ) * SIN(RADIANS($F$1)) + (B24 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>42.4300440082838</v>
+        <v>35.1135</v>
       </c>
       <c r="E24" s="22" t="n">
         <f aca="false">(( -A24 - (-0.25) ) * COS(RADIANS($F$1)) - (B24 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-126.517518376449</v>
+        <v>-93.6855</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1996,11 +2035,11 @@
       </c>
       <c r="D25" s="20" t="n">
         <f aca="false">(( -A25 - (-0.25) ) * SIN(RADIANS($F$1)) + (B25 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>43.6082892347141</v>
+        <v>35.703</v>
       </c>
       <c r="E25" s="20" t="n">
         <f aca="false">(( -A25 - (-0.25) ) * COS(RADIANS($F$1)) - (B25 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-115.298804404411</v>
+        <v>-85.24575</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2016,11 +2055,11 @@
       </c>
       <c r="D26" s="22" t="n">
         <f aca="false">(( -A26 - (-0.25) ) * SIN(RADIANS($F$1)) + (B26 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>44.2217548823404</v>
+        <v>35.874</v>
       </c>
       <c r="E26" s="22" t="n">
         <f aca="false">(( -A26 - (-0.25) ) * COS(RADIANS($F$1)) - (B26 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-104.264492241925</v>
+        <v>-76.959</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2036,11 +2075,11 @@
       </c>
       <c r="D27" s="20" t="n">
         <f aca="false">(( -A27 - (-0.25) ) * SIN(RADIANS($F$1)) + (B27 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>44.2263725666257</v>
+        <v>35.595</v>
       </c>
       <c r="E27" s="20" t="n">
         <f aca="false">(( -A27 - (-0.25) ) * COS(RADIANS($F$1)) - (B27 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-93.473079559751</v>
+        <v>-68.87025</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2056,11 +2095,11 @@
       </c>
       <c r="D28" s="22" t="n">
         <f aca="false">(( -A28 - (-0.25) ) * SIN(RADIANS($F$1)) + (B28 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>43.6112631973051</v>
+        <v>34.85925</v>
       </c>
       <c r="E28" s="22" t="n">
         <f aca="false">(( -A28 - (-0.25) ) * COS(RADIANS($F$1)) - (B28 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-82.978219367077</v>
+        <v>-61.02</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2076,11 +2115,11 @@
       </c>
       <c r="D29" s="20" t="n">
         <f aca="false">(( -A29 - (-0.25) ) * SIN(RADIANS($F$1)) + (B29 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>42.377016881587</v>
+        <v>33.669</v>
       </c>
       <c r="E29" s="20" t="n">
         <f aca="false">(( -A29 - (-0.25) ) * COS(RADIANS($F$1)) - (B29 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-72.8489743294576</v>
+        <v>-53.46</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2096,11 +2135,11 @@
       </c>
       <c r="D30" s="22" t="n">
         <f aca="false">(( -A30 - (-0.25) ) * SIN(RADIANS($F$1)) + (B30 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>40.5515213744799</v>
+        <v>32.04675</v>
       </c>
       <c r="E30" s="22" t="n">
         <f aca="false">(( -A30 - (-0.25) ) * COS(RADIANS($F$1)) - (B30 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-63.1463548814152</v>
+        <v>-46.23525</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2116,11 +2155,11 @@
       </c>
       <c r="D31" s="20" t="n">
         <f aca="false">(( -A31 - (-0.25) ) * SIN(RADIANS($F$1)) + (B31 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>38.1749712163867</v>
+        <v>30.024</v>
       </c>
       <c r="E31" s="20" t="n">
         <f aca="false">(( -A31 - (-0.25) ) * COS(RADIANS($F$1)) - (B31 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-53.9227957339891</v>
+        <v>-39.384</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2136,11 +2175,11 @@
       </c>
       <c r="D32" s="22" t="n">
         <f aca="false">(( -A32 - (-0.25) ) * SIN(RADIANS($F$1)) + (B32 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>35.3199126540615</v>
+        <v>27.657</v>
       </c>
       <c r="E32" s="22" t="n">
         <f aca="false">(( -A32 - (-0.25) ) * COS(RADIANS($F$1)) - (B32 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-45.2498723164964</v>
+        <v>-32.958</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2156,11 +2195,11 @@
       </c>
       <c r="D33" s="20" t="n">
         <f aca="false">(( -A33 - (-0.25) ) * SIN(RADIANS($F$1)) + (B33 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>32.0534190817465</v>
+        <v>24.9975</v>
       </c>
       <c r="E33" s="20" t="n">
         <f aca="false">(( -A33 - (-0.25) ) * COS(RADIANS($F$1)) - (B33 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-37.1839597988686</v>
+        <v>-26.99775</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2176,11 +2215,11 @@
       </c>
       <c r="D34" s="22" t="n">
         <f aca="false">(( -A34 - (-0.25) ) * SIN(RADIANS($F$1)) + (B34 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>28.4574500575995</v>
+        <v>22.1085</v>
       </c>
       <c r="E34" s="22" t="n">
         <f aca="false">(( -A34 - (-0.25) ) * COS(RADIANS($F$1)) - (B34 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-29.7849550159687</v>
+        <v>-21.546</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2196,11 +2235,11 @@
       </c>
       <c r="D35" s="20" t="n">
         <f aca="false">(( -A35 - (-0.25) ) * SIN(RADIANS($F$1)) + (B35 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>24.5872956829186</v>
+        <v>19.03275</v>
       </c>
       <c r="E35" s="20" t="n">
         <f aca="false">(( -A35 - (-0.25) ) * COS(RADIANS($F$1)) - (B35 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-23.1028179988058</v>
+        <v>-16.63875</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2216,11 +2255,11 @@
       </c>
       <c r="D36" s="22" t="n">
         <f aca="false">(( -A36 - (-0.25) ) * SIN(RADIANS($F$1)) + (B36 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>20.5046611979249</v>
+        <v>15.8175</v>
       </c>
       <c r="E36" s="22" t="n">
         <f aca="false">(( -A36 - (-0.25) ) * COS(RADIANS($F$1)) - (B36 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-17.1757254854448</v>
+        <v>-12.303</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2236,11 +2275,11 @@
       </c>
       <c r="D37" s="20" t="n">
         <f aca="false">(( -A37 - (-0.25) ) * SIN(RADIANS($F$1)) + (B37 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>16.3188038085757</v>
+        <v>12.546</v>
       </c>
       <c r="E37" s="20" t="n">
         <f aca="false">(( -A37 - (-0.25) ) * COS(RADIANS($F$1)) - (B37 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-12.0555220797166</v>
+        <v>-8.57475</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2256,11 +2295,11 @@
       </c>
       <c r="D38" s="22" t="n">
         <f aca="false">(( -A38 - (-0.25) ) * SIN(RADIANS($F$1)) + (B38 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>12.1726935075509</v>
+        <v>9.32625</v>
       </c>
       <c r="E38" s="22" t="n">
         <f aca="false">(( -A38 - (-0.25) ) * COS(RADIANS($F$1)) - (B38 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-7.7742168614758</v>
+        <v>-5.47425</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2276,11 +2315,11 @@
       </c>
       <c r="D39" s="20" t="n">
         <f aca="false">(( -A39 - (-0.25) ) * SIN(RADIANS($F$1)) + (B39 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>8.16185302028379</v>
+        <v>6.23025</v>
       </c>
       <c r="E39" s="20" t="n">
         <f aca="false">(( -A39 - (-0.25) ) * COS(RADIANS($F$1)) - (B39 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-4.34715287233015</v>
+        <v>-3.0105</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2296,11 +2335,11 @@
       </c>
       <c r="D40" s="22" t="n">
         <f aca="false">(( -A40 - (-0.25) ) * SIN(RADIANS($F$1)) + (B40 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>4.49385105366605</v>
+        <v>3.4155</v>
       </c>
       <c r="E40" s="22" t="n">
         <f aca="false">(( -A40 - (-0.25) ) * COS(RADIANS($F$1)) - (B40 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-1.84761880117041</v>
+        <v>-1.233</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2316,11 +2355,11 @@
       </c>
       <c r="D41" s="20" t="n">
         <f aca="false">(( -A41 - (-0.25) ) * SIN(RADIANS($F$1)) + (B41 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>1.54279289315714</v>
+        <v>1.1655</v>
       </c>
       <c r="E41" s="20" t="n">
         <f aca="false">(( -A41 - (-0.25) ) * COS(RADIANS($F$1)) - (B41 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-0.393742694587124</v>
+        <v>-0.220500000000002</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2336,11 +2375,11 @@
       </c>
       <c r="D42" s="22" t="n">
         <f aca="false">(( -A42 - (-0.25) ) * SIN(RADIANS($F$1)) + (B42 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>-0.0629616221022028</v>
+        <v>-0.04725</v>
       </c>
       <c r="E42" s="22" t="n">
         <f aca="false">(( -A42 - (-0.25) ) * COS(RADIANS($F$1)) - (B42 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-0.0434893052755625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2356,11 +2395,11 @@
       </c>
       <c r="D43" s="20" t="n">
         <f aca="false">(( -A43 - (-0.25) ) * SIN(RADIANS($F$1)) + (B43 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>-1.31446548129046</v>
+        <v>-0.97875</v>
       </c>
       <c r="E43" s="20" t="n">
         <f aca="false">(( -A43 - (-0.25) ) * COS(RADIANS($F$1)) - (B43 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-0.29396503351467</v>
+        <v>-0.220500000000002</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2376,11 +2415,11 @@
       </c>
       <c r="D44" s="22" t="n">
         <f aca="false">(( -A44 - (-0.25) ) * SIN(RADIANS($F$1)) + (B44 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>-2.416936515171</v>
+        <v>-1.77075</v>
       </c>
       <c r="E44" s="22" t="n">
         <f aca="false">(( -A44 - (-0.25) ) * COS(RADIANS($F$1)) - (B44 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-1.60628878147261</v>
+        <v>-1.233</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2396,11 +2435,11 @@
       </c>
       <c r="D45" s="20" t="n">
         <f aca="false">(( -A45 - (-0.25) ) * SIN(RADIANS($F$1)) + (B45 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>-2.75149481076474</v>
+        <v>-1.95975</v>
       </c>
       <c r="E45" s="20" t="n">
         <f aca="false">(( -A45 - (-0.25) ) * COS(RADIANS($F$1)) - (B45 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-3.96605036833884</v>
+        <v>-3.0105</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2416,11 +2455,11 @@
       </c>
       <c r="D46" s="22" t="n">
         <f aca="false">(( -A46 - (-0.25) ) * SIN(RADIANS($F$1)) + (B46 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>-2.51535347714875</v>
+        <v>-1.6965</v>
       </c>
       <c r="E46" s="22" t="n">
         <f aca="false">(( -A46 - (-0.25) ) * COS(RADIANS($F$1)) - (B46 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-7.26129895843914</v>
+        <v>-5.47425</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2436,11 +2475,11 @@
       </c>
       <c r="D47" s="20" t="n">
         <f aca="false">(( -A47 - (-0.25) ) * SIN(RADIANS($F$1)) + (B47 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>-2.01502091308957</v>
+        <v>-1.21275</v>
       </c>
       <c r="E47" s="20" t="n">
         <f aca="false">(( -A47 - (-0.25) ) * COS(RADIANS($F$1)) - (B47 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-11.4152908127092</v>
+        <v>-8.57475</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2456,11 +2495,11 @@
       </c>
       <c r="D48" s="22" t="n">
         <f aca="false">(( -A48 - (-0.25) ) * SIN(RADIANS($F$1)) + (B48 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>-1.44795770837655</v>
+        <v>-0.657</v>
       </c>
       <c r="E48" s="22" t="n">
         <f aca="false">(( -A48 - (-0.25) ) * COS(RADIANS($F$1)) - (B48 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-16.4091231408777</v>
+        <v>-12.303</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2476,11 +2515,11 @@
       </c>
       <c r="D49" s="20" t="n">
         <f aca="false">(( -A49 - (-0.25) ) * SIN(RADIANS($F$1)) + (B49 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>-0.840205128928244</v>
+        <v>-0.0495</v>
       </c>
       <c r="E49" s="20" t="n">
         <f aca="false">(( -A49 - (-0.25) ) * COS(RADIANS($F$1)) - (B49 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-22.2148701042041</v>
+        <v>-16.63875</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2496,11 +2535,11 @@
       </c>
       <c r="D50" s="22" t="n">
         <f aca="false">(( -A50 - (-0.25) ) * SIN(RADIANS($F$1)) + (B50 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>-0.193086171383981</v>
+        <v>0.6075</v>
       </c>
       <c r="E50" s="22" t="n">
         <f aca="false">(( -A50 - (-0.25) ) * COS(RADIANS($F$1)) - (B50 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-28.7844562445014</v>
+        <v>-21.546</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2516,11 +2555,11 @@
       </c>
       <c r="D51" s="20" t="n">
         <f aca="false">(( -A51 - (-0.25) ) * SIN(RADIANS($F$1)) + (B51 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>0.494655546137529</v>
+        <v>1.314</v>
       </c>
       <c r="E51" s="20" t="n">
         <f aca="false">(( -A51 - (-0.25) ) * COS(RADIANS($F$1)) - (B51 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-36.081903491997</v>
+        <v>-26.99775</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2536,11 +2575,11 @@
       </c>
       <c r="D52" s="22" t="n">
         <f aca="false">(( -A52 - (-0.25) ) * SIN(RADIANS($F$1)) + (B52 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>1.22769337195906</v>
+        <v>2.07225</v>
       </c>
       <c r="E52" s="22" t="n">
         <f aca="false">(( -A52 - (-0.25) ) * COS(RADIANS($F$1)) - (B52 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-44.059345785484</v>
+        <v>-32.958</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2556,11 +2595,11 @@
       </c>
       <c r="D53" s="20" t="n">
         <f aca="false">(( -A53 - (-0.25) ) * SIN(RADIANS($F$1)) + (B53 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>2.00202023243054</v>
+        <v>2.87775</v>
       </c>
       <c r="E53" s="20" t="n">
         <f aca="false">(( -A53 - (-0.25) ) * COS(RADIANS($F$1)) - (B53 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-52.6596084508421</v>
+        <v>-39.384</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2576,11 +2615,11 @@
       </c>
       <c r="D54" s="22" t="n">
         <f aca="false">(( -A54 - (-0.25) ) * SIN(RADIANS($F$1)) + (B54 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>2.7985334930065</v>
+        <v>3.71475</v>
       </c>
       <c r="E54" s="22" t="n">
         <f aca="false">(( -A54 - (-0.25) ) * COS(RADIANS($F$1)) - (B54 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-61.8279914939815</v>
+        <v>-46.23525</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2596,11 +2635,11 @@
       </c>
       <c r="D55" s="20" t="n">
         <f aca="false">(( -A55 - (-0.25) ) * SIN(RADIANS($F$1)) + (B55 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>3.59865401159202</v>
+        <v>4.5675</v>
       </c>
       <c r="E55" s="20" t="n">
         <f aca="false">(( -A55 - (-0.25) ) * COS(RADIANS($F$1)) - (B55 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-71.4948040584072</v>
+        <v>-53.46</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2616,11 +2655,11 @@
       </c>
       <c r="D56" s="22" t="n">
         <f aca="false">(( -A56 - (-0.25) ) * SIN(RADIANS($F$1)) + (B56 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>4.38617262763258</v>
+        <v>5.4225</v>
       </c>
       <c r="E56" s="22" t="n">
         <f aca="false">(( -A56 - (-0.25) ) * COS(RADIANS($F$1)) - (B56 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-81.6084490210005</v>
+        <v>-61.02</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2636,11 +2675,11 @@
       </c>
       <c r="D57" s="20" t="n">
         <f aca="false">(( -A57 - (-0.25) ) * SIN(RADIANS($F$1)) + (B57 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>5.14819244852505</v>
+        <v>6.2685</v>
       </c>
       <c r="E57" s="20" t="n">
         <f aca="false">(( -A57 - (-0.25) ) * COS(RADIANS($F$1)) - (B57 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-92.1084394396898</v>
+        <v>-68.87025</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2656,11 +2695,11 @@
       </c>
       <c r="D58" s="22" t="n">
         <f aca="false">(( -A58 - (-0.25) ) * SIN(RADIANS($F$1)) + (B58 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>5.86913250465554</v>
+        <v>7.092</v>
       </c>
       <c r="E58" s="22" t="n">
         <f aca="false">(( -A58 - (-0.25) ) * COS(RADIANS($F$1)) - (B58 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-102.92518915647</v>
+        <v>-76.959</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2676,11 +2715,11 @@
       </c>
       <c r="D59" s="20" t="n">
         <f aca="false">(( -A59 - (-0.25) ) * SIN(RADIANS($F$1)) + (B59 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>6.53588650644072</v>
+        <v>7.88175</v>
       </c>
       <c r="E59" s="20" t="n">
         <f aca="false">(( -A59 - (-0.25) ) * COS(RADIANS($F$1)) - (B59 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-114.004207574232</v>
+        <v>-85.24575</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2696,11 +2735,11 @@
       </c>
       <c r="D60" s="22" t="n">
         <f aca="false">(( -A60 - (-0.25) ) * SIN(RADIANS($F$1)) + (B60 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>7.12956121631532</v>
+        <v>8.622</v>
       </c>
       <c r="E60" s="22" t="n">
         <f aca="false">(( -A60 - (-0.25) ) * COS(RADIANS($F$1)) - (B60 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-125.284798353923</v>
+        <v>-93.6855</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2716,11 +2755,11 @@
       </c>
       <c r="D61" s="20" t="n">
         <f aca="false">(( -A61 - (-0.25) ) * SIN(RADIANS($F$1)) + (B61 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>7.63746913865643</v>
+        <v>9.3015</v>
       </c>
       <c r="E61" s="20" t="n">
         <f aca="false">(( -A61 - (-0.25) ) * COS(RADIANS($F$1)) - (B61 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-136.70047820851</v>
+        <v>-102.22875</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2736,11 +2775,11 @@
       </c>
       <c r="D62" s="22" t="n">
         <f aca="false">(( -A62 - (-0.25) ) * SIN(RADIANS($F$1)) + (B62 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>8.03398780150593</v>
+        <v>9.9</v>
       </c>
       <c r="E62" s="22" t="n">
         <f aca="false">(( -A62 - (-0.25) ) * COS(RADIANS($F$1)) - (B62 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-148.211328609328</v>
+        <v>-110.84625</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2756,11 +2795,11 @@
       </c>
       <c r="D63" s="20" t="n">
         <f aca="false">(( -A63 - (-0.25) ) * SIN(RADIANS($F$1)) + (B63 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>8.3041644261906</v>
+        <v>10.404</v>
       </c>
       <c r="E63" s="20" t="n">
         <f aca="false">(( -A63 - (-0.25) ) * COS(RADIANS($F$1)) - (B63 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-159.729774363486</v>
+        <v>-119.47275</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2776,11 +2815,11 @@
       </c>
       <c r="D64" s="22" t="n">
         <f aca="false">(( -A64 - (-0.25) ) * SIN(RADIANS($F$1)) + (B64 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>8.43300815030514</v>
+        <v>10.80225</v>
       </c>
       <c r="E64" s="22" t="n">
         <f aca="false">(( -A64 - (-0.25) ) * COS(RADIANS($F$1)) - (B64 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-171.255291978533</v>
+        <v>-128.10825</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2796,11 +2835,11 @@
       </c>
       <c r="D65" s="20" t="n">
         <f aca="false">(( -A65 - (-0.25) ) * SIN(RADIANS($F$1)) + (B65 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>8.40263463745333</v>
+        <v>11.08125</v>
       </c>
       <c r="E65" s="20" t="n">
         <f aca="false">(( -A65 - (-0.25) ) * COS(RADIANS($F$1)) - (B65 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-182.784255091047</v>
+        <v>-136.7505</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2816,11 +2855,11 @@
       </c>
       <c r="D66" s="22" t="n">
         <f aca="false">(( -A66 - (-0.25) ) * SIN(RADIANS($F$1)) + (B66 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>8.20398275543393</v>
+        <v>11.232</v>
       </c>
       <c r="E66" s="22" t="n">
         <f aca="false">(( -A66 - (-0.25) ) * COS(RADIANS($F$1)) - (B66 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-194.232296077599</v>
+        <v>-145.3365</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2836,11 +2875,11 @@
       </c>
       <c r="D67" s="20" t="n">
         <f aca="false">(( -A67 - (-0.25) ) * SIN(RADIANS($F$1)) + (B67 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>7.82478380258447</v>
+        <v>11.24325</v>
       </c>
       <c r="E67" s="20" t="n">
         <f aca="false">(( -A67 - (-0.25) ) * COS(RADIANS($F$1)) - (B67 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-205.52093896123</v>
+        <v>-153.80775</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2856,11 +2895,11 @@
       </c>
       <c r="D68" s="22" t="n">
         <f aca="false">(( -A68 - (-0.25) ) * SIN(RADIANS($F$1)) + (B68 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>7.25618604368394</v>
+        <v>11.106</v>
       </c>
       <c r="E68" s="22" t="n">
         <f aca="false">(( -A68 - (-0.25) ) * COS(RADIANS($F$1)) - (B68 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-216.559819773549</v>
+        <v>-162.09675</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2876,11 +2915,11 @@
       </c>
       <c r="D69" s="20" t="n">
         <f aca="false">(( -A69 - (-0.25) ) * SIN(RADIANS($F$1)) + (B69 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>6.49533408847344</v>
+        <v>10.81575</v>
       </c>
       <c r="E69" s="20" t="n">
         <f aca="false">(( -A69 - (-0.25) ) * COS(RADIANS($F$1)) - (B69 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-227.258783943142</v>
+        <v>-170.136</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2896,11 +2935,11 @@
       </c>
       <c r="D70" s="22" t="n">
         <f aca="false">(( -A70 - (-0.25) ) * SIN(RADIANS($F$1)) + (B70 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>5.53937254669409</v>
+        <v>10.368</v>
       </c>
       <c r="E70" s="22" t="n">
         <f aca="false">(( -A70 - (-0.25) ) * COS(RADIANS($F$1)) - (B70 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-237.5276768986</v>
+        <v>-177.858</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2916,11 +2955,11 @@
       </c>
       <c r="D71" s="20" t="n">
         <f aca="false">(( -A71 - (-0.25) ) * SIN(RADIANS($F$1)) + (B71 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>4.37645151064383</v>
+        <v>9.7515</v>
       </c>
       <c r="E71" s="20" t="n">
         <f aca="false">(( -A71 - (-0.25) ) * COS(RADIANS($F$1)) - (B71 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-247.276029973038</v>
+        <v>-185.19525</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2936,11 +2975,11 @@
       </c>
       <c r="D72" s="22" t="n">
         <f aca="false">(( -A72 - (-0.25) ) * SIN(RADIANS($F$1)) + (B72 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>2.98862002916837</v>
+        <v>8.9505</v>
       </c>
       <c r="E72" s="22" t="n">
         <f aca="false">(( -A72 - (-0.25) ) * COS(RADIANS($F$1)) - (B72 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-256.416163275076</v>
+        <v>-192.0825</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2956,11 +2995,11 @@
       </c>
       <c r="D73" s="20" t="n">
         <f aca="false">(( -A73 - (-0.25) ) * SIN(RADIANS($F$1)) + (B73 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>1.36991984103765</v>
+        <v>7.95825</v>
       </c>
       <c r="E73" s="20" t="n">
         <f aca="false">(( -A73 - (-0.25) ) * COS(RADIANS($F$1)) - (B73 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-264.860815707293</v>
+        <v>-198.4545</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2976,11 +3015,11 @@
       </c>
       <c r="D74" s="22" t="n">
         <f aca="false">(( -A74 - (-0.25) ) * SIN(RADIANS($F$1)) + (B74 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>-0.470511754082969</v>
+        <v>6.77925</v>
       </c>
       <c r="E74" s="22" t="n">
         <f aca="false">(( -A74 - (-0.25) ) * COS(RADIANS($F$1)) - (B74 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-272.520251492237</v>
+        <v>-204.24375</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2996,11 +3035,11 @@
       </c>
       <c r="D75" s="20" t="n">
         <f aca="false">(( -A75 - (-0.25) ) * SIN(RADIANS($F$1)) + (B75 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>-2.44610846447121</v>
+        <v>5.4765</v>
       </c>
       <c r="E75" s="20" t="n">
         <f aca="false">(( -A75 - (-0.25) ) * COS(RADIANS($F$1)) - (B75 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-279.322447875605</v>
+        <v>-209.394</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3016,11 +3055,11 @@
       </c>
       <c r="D76" s="22" t="n">
         <f aca="false">(( -A76 - (-0.25) ) * SIN(RADIANS($F$1)) + (B76 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>-4.40134603134047</v>
+        <v>4.16475</v>
       </c>
       <c r="E76" s="22" t="n">
         <f aca="false">(( -A76 - (-0.25) ) * COS(RADIANS($F$1)) - (B76 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-285.197790168366</v>
+        <v>-213.849</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3036,11 +3075,11 @@
       </c>
       <c r="D77" s="20" t="n">
         <f aca="false">(( -A77 - (-0.25) ) * SIN(RADIANS($F$1)) + (B77 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>-6.25649209585141</v>
+        <v>2.9025</v>
       </c>
       <c r="E77" s="20" t="n">
         <f aca="false">(( -A77 - (-0.25) ) * COS(RADIANS($F$1)) - (B77 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-290.098031599084</v>
+        <v>-217.5705</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3056,11 +3095,11 @@
       </c>
       <c r="D78" s="22" t="n">
         <f aca="false">(( -A78 - (-0.25) ) * SIN(RADIANS($F$1)) + (B78 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>-7.99770747898995</v>
+        <v>1.701</v>
       </c>
       <c r="E78" s="22" t="n">
         <f aca="false">(( -A78 - (-0.25) ) * COS(RADIANS($F$1)) - (B78 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-294.056675557502</v>
+        <v>-220.58325</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3076,11 +3115,11 @@
       </c>
       <c r="D79" s="20" t="n">
         <f aca="false">(( -A79 - (-0.25) ) * SIN(RADIANS($F$1)) + (B79 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>-9.41606239349304</v>
+        <v>0.71775</v>
       </c>
       <c r="E79" s="20" t="n">
         <f aca="false">(( -A79 - (-0.25) ) * COS(RADIANS($F$1)) - (B79 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-297.108034490258</v>
+        <v>-222.9075</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3096,11 +3135,11 @@
       </c>
       <c r="D80" s="22" t="n">
         <f aca="false">(( -A80 - (-0.25) ) * SIN(RADIANS($F$1)) + (B80 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>-10.240217453472</v>
+        <v>0.153</v>
       </c>
       <c r="E80" s="22" t="n">
         <f aca="false">(( -A80 - (-0.25) ) * COS(RADIANS($F$1)) - (B80 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-299.132505146284</v>
+        <v>-224.4465</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3116,11 +3155,11 @@
       </c>
       <c r="D81" s="20" t="n">
         <f aca="false">(( -A81 - (-0.25) ) * SIN(RADIANS($F$1)) + (B81 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>-10.4698490107503</v>
+        <v>0</v>
       </c>
       <c r="E81" s="20" t="n">
         <f aca="false">(( -A81 - (-0.25) ) * COS(RADIANS($F$1)) - (B81 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-299.862936079297</v>
+        <v>-225</v>
       </c>
     </row>
   </sheetData>
@@ -3167,7 +3206,7 @@
       </c>
       <c r="E1" s="16" t="n">
         <f aca="false">Control_Panel!$C$7</f>
-        <v>180</v>
+        <v>225</v>
       </c>
       <c r="F1" s="17" t="n">
         <f aca="false">Control_Panel!$C$23</f>
@@ -3175,11 +3214,11 @@
       </c>
       <c r="G1" s="16" t="n">
         <f aca="false">Control_Panel!$C$15</f>
-        <v>550</v>
+        <v>518</v>
       </c>
       <c r="H1" s="17" t="n">
         <f aca="false">Control_Panel!$C$10</f>
-        <v>0</v>
+        <v>11.02</v>
       </c>
       <c r="I1" s="17" t="n">
         <f aca="false">Control_Panel!$C$11</f>
@@ -3224,15 +3263,15 @@
       </c>
       <c r="C3" s="20" t="n">
         <f aca="false">$G$1</f>
-        <v>550</v>
+        <v>518</v>
       </c>
       <c r="D3" s="20" t="n">
         <f aca="false">(( -A3 - (-0.25) ) * SIN(RADIANS($F$1)) + (B3 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>38.4597465689307</v>
+        <v>36.2220885867384</v>
       </c>
       <c r="E3" s="20" t="n">
         <f aca="false">(( -A3 - (-0.25) ) * COS(RADIANS($F$1)) - (B3 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-180</v>
+        <v>-325.876660887038</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3244,15 +3283,15 @@
       </c>
       <c r="C4" s="22" t="n">
         <f aca="false">$G$1</f>
-        <v>550</v>
+        <v>518</v>
       </c>
       <c r="D4" s="22" t="n">
         <f aca="false">(( -A4 - (-0.25) ) * SIN(RADIANS($F$1)) + (B4 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>38.7999465689307</v>
+        <v>36.6473385867384</v>
       </c>
       <c r="E4" s="22" t="n">
         <f aca="false">(( -A4 - (-0.25) ) * COS(RADIANS($F$1)) - (B4 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-179.5572</v>
+        <v>-325.323160887038</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3264,15 +3303,15 @@
       </c>
       <c r="C5" s="20" t="n">
         <f aca="false">$G$1</f>
-        <v>550</v>
+        <v>518</v>
       </c>
       <c r="D5" s="20" t="n">
         <f aca="false">(( -A5 - (-0.25) ) * SIN(RADIANS($F$1)) + (B5 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>39.5829465689307</v>
+        <v>37.6260885867384</v>
       </c>
       <c r="E5" s="20" t="n">
         <f aca="false">(( -A5 - (-0.25) ) * COS(RADIANS($F$1)) - (B5 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-178.326</v>
+        <v>-323.784160887038</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3284,15 +3323,15 @@
       </c>
       <c r="C6" s="22" t="n">
         <f aca="false">$G$1</f>
-        <v>550</v>
+        <v>518</v>
       </c>
       <c r="D6" s="22" t="n">
         <f aca="false">(( -A6 - (-0.25) ) * SIN(RADIANS($F$1)) + (B6 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>40.5297465689307</v>
+        <v>38.8095885867384</v>
       </c>
       <c r="E6" s="22" t="n">
         <f aca="false">(( -A6 - (-0.25) ) * COS(RADIANS($F$1)) - (B6 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-176.4666</v>
+        <v>-321.459910887038</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3304,15 +3343,15 @@
       </c>
       <c r="C7" s="20" t="n">
         <f aca="false">$G$1</f>
-        <v>550</v>
+        <v>518</v>
       </c>
       <c r="D7" s="20" t="n">
         <f aca="false">(( -A7 - (-0.25) ) * SIN(RADIANS($F$1)) + (B7 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>41.5935465689307</v>
+        <v>40.1393385867384</v>
       </c>
       <c r="E7" s="20" t="n">
         <f aca="false">(( -A7 - (-0.25) ) * COS(RADIANS($F$1)) - (B7 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-174.0564</v>
+        <v>-318.447160887038</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3324,15 +3363,15 @@
       </c>
       <c r="C8" s="22" t="n">
         <f aca="false">$G$1</f>
-        <v>550</v>
+        <v>518</v>
       </c>
       <c r="D8" s="22" t="n">
         <f aca="false">(( -A8 - (-0.25) ) * SIN(RADIANS($F$1)) + (B8 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>42.7833465689307</v>
+        <v>41.6265885867384</v>
       </c>
       <c r="E8" s="22" t="n">
         <f aca="false">(( -A8 - (-0.25) ) * COS(RADIANS($F$1)) - (B8 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-171.0792</v>
+        <v>-314.725660887038</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3344,15 +3383,15 @@
       </c>
       <c r="C9" s="20" t="n">
         <f aca="false">$G$1</f>
-        <v>550</v>
+        <v>518</v>
       </c>
       <c r="D9" s="20" t="n">
         <f aca="false">(( -A9 - (-0.25) ) * SIN(RADIANS($F$1)) + (B9 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>44.1981465689307</v>
+        <v>43.3950885867384</v>
       </c>
       <c r="E9" s="20" t="n">
         <f aca="false">(( -A9 - (-0.25) ) * COS(RADIANS($F$1)) - (B9 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-167.5152</v>
+        <v>-310.270660887038</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3364,15 +3403,15 @@
       </c>
       <c r="C10" s="22" t="n">
         <f aca="false">$G$1</f>
-        <v>550</v>
+        <v>518</v>
       </c>
       <c r="D10" s="22" t="n">
         <f aca="false">(( -A10 - (-0.25) ) * SIN(RADIANS($F$1)) + (B10 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>45.6615465689307</v>
+        <v>45.2243385867384</v>
       </c>
       <c r="E10" s="22" t="n">
         <f aca="false">(( -A10 - (-0.25) ) * COS(RADIANS($F$1)) - (B10 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-163.395</v>
+        <v>-305.120410887038</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3384,15 +3423,15 @@
       </c>
       <c r="C11" s="20" t="n">
         <f aca="false">$G$1</f>
-        <v>550</v>
+        <v>518</v>
       </c>
       <c r="D11" s="20" t="n">
         <f aca="false">(( -A11 - (-0.25) ) * SIN(RADIANS($F$1)) + (B11 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>47.1861465689307</v>
+        <v>47.1300885867384</v>
       </c>
       <c r="E11" s="20" t="n">
         <f aca="false">(( -A11 - (-0.25) ) * COS(RADIANS($F$1)) - (B11 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-158.7636</v>
+        <v>-299.331160887038</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3404,15 +3443,15 @@
       </c>
       <c r="C12" s="22" t="n">
         <f aca="false">$G$1</f>
-        <v>550</v>
+        <v>518</v>
       </c>
       <c r="D12" s="22" t="n">
         <f aca="false">(( -A12 - (-0.25) ) * SIN(RADIANS($F$1)) + (B12 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>48.7521465689307</v>
+        <v>49.0875885867384</v>
       </c>
       <c r="E12" s="22" t="n">
         <f aca="false">(( -A12 - (-0.25) ) * COS(RADIANS($F$1)) - (B12 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-153.666</v>
+        <v>-292.959160887038</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3424,15 +3463,15 @@
       </c>
       <c r="C13" s="20" t="n">
         <f aca="false">$G$1</f>
-        <v>550</v>
+        <v>518</v>
       </c>
       <c r="D13" s="20" t="n">
         <f aca="false">(( -A13 - (-0.25) ) * SIN(RADIANS($F$1)) + (B13 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>50.3685465689307</v>
+        <v>51.1080885867384</v>
       </c>
       <c r="E13" s="20" t="n">
         <f aca="false">(( -A13 - (-0.25) ) * COS(RADIANS($F$1)) - (B13 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-148.1562</v>
+        <v>-286.071910887038</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3444,15 +3483,15 @@
       </c>
       <c r="C14" s="22" t="n">
         <f aca="false">$G$1</f>
-        <v>550</v>
+        <v>518</v>
       </c>
       <c r="D14" s="22" t="n">
         <f aca="false">(( -A14 - (-0.25) ) * SIN(RADIANS($F$1)) + (B14 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>52.0479465689307</v>
+        <v>53.2073385867384</v>
       </c>
       <c r="E14" s="22" t="n">
         <f aca="false">(( -A14 - (-0.25) ) * COS(RADIANS($F$1)) - (B14 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-142.2864</v>
+        <v>-278.734660887038</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3464,15 +3503,15 @@
       </c>
       <c r="C15" s="20" t="n">
         <f aca="false">$G$1</f>
-        <v>550</v>
+        <v>518</v>
       </c>
       <c r="D15" s="20" t="n">
         <f aca="false">(( -A15 - (-0.25) ) * SIN(RADIANS($F$1)) + (B15 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>53.7777465689307</v>
+        <v>55.3695885867384</v>
       </c>
       <c r="E15" s="20" t="n">
         <f aca="false">(( -A15 - (-0.25) ) * COS(RADIANS($F$1)) - (B15 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-136.1088</v>
+        <v>-271.012660887038</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3484,15 +3523,15 @@
       </c>
       <c r="C16" s="22" t="n">
         <f aca="false">$G$1</f>
-        <v>550</v>
+        <v>518</v>
       </c>
       <c r="D16" s="22" t="n">
         <f aca="false">(( -A16 - (-0.25) ) * SIN(RADIANS($F$1)) + (B16 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>55.5273465689307</v>
+        <v>57.5565885867384</v>
       </c>
       <c r="E16" s="22" t="n">
         <f aca="false">(( -A16 - (-0.25) ) * COS(RADIANS($F$1)) - (B16 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-129.6774</v>
+        <v>-262.973410887038</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3504,15 +3543,15 @@
       </c>
       <c r="C17" s="20" t="n">
         <f aca="false">$G$1</f>
-        <v>550</v>
+        <v>518</v>
       </c>
       <c r="D17" s="20" t="n">
         <f aca="false">(( -A17 - (-0.25) ) * SIN(RADIANS($F$1)) + (B17 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>57.2625465689307</v>
+        <v>59.7255885867384</v>
       </c>
       <c r="E17" s="20" t="n">
         <f aca="false">(( -A17 - (-0.25) ) * COS(RADIANS($F$1)) - (B17 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-123.0462</v>
+        <v>-254.684410887038</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3524,15 +3563,15 @@
       </c>
       <c r="C18" s="22" t="n">
         <f aca="false">$G$1</f>
-        <v>550</v>
+        <v>518</v>
       </c>
       <c r="D18" s="22" t="n">
         <f aca="false">(( -A18 - (-0.25) ) * SIN(RADIANS($F$1)) + (B18 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>58.9527465689307</v>
+        <v>61.8383385867384</v>
       </c>
       <c r="E18" s="22" t="n">
         <f aca="false">(( -A18 - (-0.25) ) * COS(RADIANS($F$1)) - (B18 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-116.2692</v>
+        <v>-246.213160887038</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3544,15 +3583,15 @@
       </c>
       <c r="C19" s="20" t="n">
         <f aca="false">$G$1</f>
-        <v>550</v>
+        <v>518</v>
       </c>
       <c r="D19" s="20" t="n">
         <f aca="false">(( -A19 - (-0.25) ) * SIN(RADIANS($F$1)) + (B19 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>60.5763465689307</v>
+        <v>63.8678385867384</v>
       </c>
       <c r="E19" s="20" t="n">
         <f aca="false">(( -A19 - (-0.25) ) * COS(RADIANS($F$1)) - (B19 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-109.4004</v>
+        <v>-237.627160887038</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3564,15 +3603,15 @@
       </c>
       <c r="C20" s="22" t="n">
         <f aca="false">$G$1</f>
-        <v>550</v>
+        <v>518</v>
       </c>
       <c r="D20" s="22" t="n">
         <f aca="false">(( -A20 - (-0.25) ) * SIN(RADIANS($F$1)) + (B20 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>62.1063465689307</v>
+        <v>65.7803385867384</v>
       </c>
       <c r="E20" s="22" t="n">
         <f aca="false">(( -A20 - (-0.25) ) * COS(RADIANS($F$1)) - (B20 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-102.4866</v>
+        <v>-228.984910887038</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3584,15 +3623,15 @@
       </c>
       <c r="C21" s="20" t="n">
         <f aca="false">$G$1</f>
-        <v>550</v>
+        <v>518</v>
       </c>
       <c r="D21" s="20" t="n">
         <f aca="false">(( -A21 - (-0.25) ) * SIN(RADIANS($F$1)) + (B21 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>63.5085465689307</v>
+        <v>67.5330885867384</v>
       </c>
       <c r="E21" s="20" t="n">
         <f aca="false">(( -A21 - (-0.25) ) * COS(RADIANS($F$1)) - (B21 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-95.5782</v>
+        <v>-220.349410887038</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3604,15 +3643,15 @@
       </c>
       <c r="C22" s="22" t="n">
         <f aca="false">$G$1</f>
-        <v>550</v>
+        <v>518</v>
       </c>
       <c r="D22" s="22" t="n">
         <f aca="false">(( -A22 - (-0.25) ) * SIN(RADIANS($F$1)) + (B22 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>64.7469465689307</v>
+        <v>69.0810885867384</v>
       </c>
       <c r="E22" s="22" t="n">
         <f aca="false">(( -A22 - (-0.25) ) * COS(RADIANS($F$1)) - (B22 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-88.677</v>
+        <v>-211.722910887038</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3624,15 +3663,15 @@
       </c>
       <c r="C23" s="20" t="n">
         <f aca="false">$G$1</f>
-        <v>550</v>
+        <v>518</v>
       </c>
       <c r="D23" s="20" t="n">
         <f aca="false">(( -A23 - (-0.25) ) * SIN(RADIANS($F$1)) + (B23 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>65.7783465689307</v>
+        <v>70.3703385867384</v>
       </c>
       <c r="E23" s="20" t="n">
         <f aca="false">(( -A23 - (-0.25) ) * COS(RADIANS($F$1)) - (B23 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-81.783</v>
+        <v>-203.105410887038</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3644,15 +3683,15 @@
       </c>
       <c r="C24" s="22" t="n">
         <f aca="false">$G$1</f>
-        <v>550</v>
+        <v>518</v>
       </c>
       <c r="D24" s="22" t="n">
         <f aca="false">(( -A24 - (-0.25) ) * SIN(RADIANS($F$1)) + (B24 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>66.5505465689307</v>
+        <v>71.3355885867384</v>
       </c>
       <c r="E24" s="22" t="n">
         <f aca="false">(( -A24 - (-0.25) ) * COS(RADIANS($F$1)) - (B24 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-74.9484</v>
+        <v>-194.562160887038</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3664,15 +3703,15 @@
       </c>
       <c r="C25" s="20" t="n">
         <f aca="false">$G$1</f>
-        <v>550</v>
+        <v>518</v>
       </c>
       <c r="D25" s="20" t="n">
         <f aca="false">(( -A25 - (-0.25) ) * SIN(RADIANS($F$1)) + (B25 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>67.0221465689307</v>
+        <v>71.9250885867384</v>
       </c>
       <c r="E25" s="20" t="n">
         <f aca="false">(( -A25 - (-0.25) ) * COS(RADIANS($F$1)) - (B25 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-68.1966</v>
+        <v>-186.122410887038</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3684,15 +3723,15 @@
       </c>
       <c r="C26" s="22" t="n">
         <f aca="false">$G$1</f>
-        <v>550</v>
+        <v>518</v>
       </c>
       <c r="D26" s="22" t="n">
         <f aca="false">(( -A26 - (-0.25) ) * SIN(RADIANS($F$1)) + (B26 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>67.1589465689307</v>
+        <v>72.0960885867384</v>
       </c>
       <c r="E26" s="22" t="n">
         <f aca="false">(( -A26 - (-0.25) ) * COS(RADIANS($F$1)) - (B26 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-61.5672</v>
+        <v>-177.835660887038</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3704,15 +3743,15 @@
       </c>
       <c r="C27" s="20" t="n">
         <f aca="false">$G$1</f>
-        <v>550</v>
+        <v>518</v>
       </c>
       <c r="D27" s="20" t="n">
         <f aca="false">(( -A27 - (-0.25) ) * SIN(RADIANS($F$1)) + (B27 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>66.9357465689307</v>
+        <v>71.8170885867384</v>
       </c>
       <c r="E27" s="20" t="n">
         <f aca="false">(( -A27 - (-0.25) ) * COS(RADIANS($F$1)) - (B27 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-55.0962</v>
+        <v>-169.746910887038</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3724,15 +3763,15 @@
       </c>
       <c r="C28" s="22" t="n">
         <f aca="false">$G$1</f>
-        <v>550</v>
+        <v>518</v>
       </c>
       <c r="D28" s="22" t="n">
         <f aca="false">(( -A28 - (-0.25) ) * SIN(RADIANS($F$1)) + (B28 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>66.3471465689307</v>
+        <v>71.0813385867384</v>
       </c>
       <c r="E28" s="22" t="n">
         <f aca="false">(( -A28 - (-0.25) ) * COS(RADIANS($F$1)) - (B28 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-48.816</v>
+        <v>-161.896660887038</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3744,15 +3783,15 @@
       </c>
       <c r="C29" s="20" t="n">
         <f aca="false">$G$1</f>
-        <v>550</v>
+        <v>518</v>
       </c>
       <c r="D29" s="20" t="n">
         <f aca="false">(( -A29 - (-0.25) ) * SIN(RADIANS($F$1)) + (B29 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>65.3949465689307</v>
+        <v>69.8910885867384</v>
       </c>
       <c r="E29" s="20" t="n">
         <f aca="false">(( -A29 - (-0.25) ) * COS(RADIANS($F$1)) - (B29 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-42.768</v>
+        <v>-154.336660887038</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3764,15 +3803,15 @@
       </c>
       <c r="C30" s="22" t="n">
         <f aca="false">$G$1</f>
-        <v>550</v>
+        <v>518</v>
       </c>
       <c r="D30" s="22" t="n">
         <f aca="false">(( -A30 - (-0.25) ) * SIN(RADIANS($F$1)) + (B30 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>64.0971465689307</v>
+        <v>68.2688385867384</v>
       </c>
       <c r="E30" s="22" t="n">
         <f aca="false">(( -A30 - (-0.25) ) * COS(RADIANS($F$1)) - (B30 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-36.9882</v>
+        <v>-147.111910887038</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3784,15 +3823,15 @@
       </c>
       <c r="C31" s="20" t="n">
         <f aca="false">$G$1</f>
-        <v>550</v>
+        <v>518</v>
       </c>
       <c r="D31" s="20" t="n">
         <f aca="false">(( -A31 - (-0.25) ) * SIN(RADIANS($F$1)) + (B31 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>62.4789465689307</v>
+        <v>66.2460885867384</v>
       </c>
       <c r="E31" s="20" t="n">
         <f aca="false">(( -A31 - (-0.25) ) * COS(RADIANS($F$1)) - (B31 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-31.5072</v>
+        <v>-140.260660887038</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3804,15 +3843,15 @@
       </c>
       <c r="C32" s="22" t="n">
         <f aca="false">$G$1</f>
-        <v>550</v>
+        <v>518</v>
       </c>
       <c r="D32" s="22" t="n">
         <f aca="false">(( -A32 - (-0.25) ) * SIN(RADIANS($F$1)) + (B32 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>60.5853465689307</v>
+        <v>63.8790885867384</v>
       </c>
       <c r="E32" s="22" t="n">
         <f aca="false">(( -A32 - (-0.25) ) * COS(RADIANS($F$1)) - (B32 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-26.3664</v>
+        <v>-133.834660887038</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3824,15 +3863,15 @@
       </c>
       <c r="C33" s="20" t="n">
         <f aca="false">$G$1</f>
-        <v>550</v>
+        <v>518</v>
       </c>
       <c r="D33" s="20" t="n">
         <f aca="false">(( -A33 - (-0.25) ) * SIN(RADIANS($F$1)) + (B33 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>58.4577465689307</v>
+        <v>61.2195885867384</v>
       </c>
       <c r="E33" s="20" t="n">
         <f aca="false">(( -A33 - (-0.25) ) * COS(RADIANS($F$1)) - (B33 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-21.5982</v>
+        <v>-127.874410887038</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3844,15 +3883,15 @@
       </c>
       <c r="C34" s="22" t="n">
         <f aca="false">$G$1</f>
-        <v>550</v>
+        <v>518</v>
       </c>
       <c r="D34" s="22" t="n">
         <f aca="false">(( -A34 - (-0.25) ) * SIN(RADIANS($F$1)) + (B34 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>56.1465465689307</v>
+        <v>58.3305885867384</v>
       </c>
       <c r="E34" s="22" t="n">
         <f aca="false">(( -A34 - (-0.25) ) * COS(RADIANS($F$1)) - (B34 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-17.2368</v>
+        <v>-122.422660887038</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3864,15 +3903,15 @@
       </c>
       <c r="C35" s="20" t="n">
         <f aca="false">$G$1</f>
-        <v>550</v>
+        <v>518</v>
       </c>
       <c r="D35" s="20" t="n">
         <f aca="false">(( -A35 - (-0.25) ) * SIN(RADIANS($F$1)) + (B35 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>53.6859465689307</v>
+        <v>55.2548385867384</v>
       </c>
       <c r="E35" s="20" t="n">
         <f aca="false">(( -A35 - (-0.25) ) * COS(RADIANS($F$1)) - (B35 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-13.311</v>
+        <v>-117.515410887038</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3884,15 +3923,15 @@
       </c>
       <c r="C36" s="22" t="n">
         <f aca="false">$G$1</f>
-        <v>550</v>
+        <v>518</v>
       </c>
       <c r="D36" s="22" t="n">
         <f aca="false">(( -A36 - (-0.25) ) * SIN(RADIANS($F$1)) + (B36 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>51.1137465689307</v>
+        <v>52.0395885867384</v>
       </c>
       <c r="E36" s="22" t="n">
         <f aca="false">(( -A36 - (-0.25) ) * COS(RADIANS($F$1)) - (B36 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-9.8424</v>
+        <v>-113.179660887038</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3904,15 +3943,15 @@
       </c>
       <c r="C37" s="20" t="n">
         <f aca="false">$G$1</f>
-        <v>550</v>
+        <v>518</v>
       </c>
       <c r="D37" s="20" t="n">
         <f aca="false">(( -A37 - (-0.25) ) * SIN(RADIANS($F$1)) + (B37 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>48.4965465689307</v>
+        <v>48.7680885867384</v>
       </c>
       <c r="E37" s="20" t="n">
         <f aca="false">(( -A37 - (-0.25) ) * COS(RADIANS($F$1)) - (B37 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-6.8598</v>
+        <v>-109.451410887038</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3924,15 +3963,15 @@
       </c>
       <c r="C38" s="22" t="n">
         <f aca="false">$G$1</f>
-        <v>550</v>
+        <v>518</v>
       </c>
       <c r="D38" s="22" t="n">
         <f aca="false">(( -A38 - (-0.25) ) * SIN(RADIANS($F$1)) + (B38 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>45.9207465689307</v>
+        <v>45.5483385867384</v>
       </c>
       <c r="E38" s="22" t="n">
         <f aca="false">(( -A38 - (-0.25) ) * COS(RADIANS($F$1)) - (B38 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-4.3794</v>
+        <v>-106.350910887038</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3944,15 +3983,15 @@
       </c>
       <c r="C39" s="20" t="n">
         <f aca="false">$G$1</f>
-        <v>550</v>
+        <v>518</v>
       </c>
       <c r="D39" s="20" t="n">
         <f aca="false">(( -A39 - (-0.25) ) * SIN(RADIANS($F$1)) + (B39 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>43.4439465689307</v>
+        <v>42.4523385867384</v>
       </c>
       <c r="E39" s="20" t="n">
         <f aca="false">(( -A39 - (-0.25) ) * COS(RADIANS($F$1)) - (B39 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-2.4084</v>
+        <v>-103.887160887038</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3964,15 +4003,15 @@
       </c>
       <c r="C40" s="22" t="n">
         <f aca="false">$G$1</f>
-        <v>550</v>
+        <v>518</v>
       </c>
       <c r="D40" s="22" t="n">
         <f aca="false">(( -A40 - (-0.25) ) * SIN(RADIANS($F$1)) + (B40 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>41.1921465689307</v>
+        <v>39.6375885867384</v>
       </c>
       <c r="E40" s="22" t="n">
         <f aca="false">(( -A40 - (-0.25) ) * COS(RADIANS($F$1)) - (B40 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-0.986400000000002</v>
+        <v>-102.109660887038</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3984,15 +4023,15 @@
       </c>
       <c r="C41" s="20" t="n">
         <f aca="false">$G$1</f>
-        <v>550</v>
+        <v>518</v>
       </c>
       <c r="D41" s="20" t="n">
         <f aca="false">(( -A41 - (-0.25) ) * SIN(RADIANS($F$1)) + (B41 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>39.3921465689307</v>
+        <v>37.3875885867384</v>
       </c>
       <c r="E41" s="20" t="n">
         <f aca="false">(( -A41 - (-0.25) ) * COS(RADIANS($F$1)) - (B41 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-0.176400000000002</v>
+        <v>-101.097160887038</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4004,15 +4043,15 @@
       </c>
       <c r="C42" s="22" t="n">
         <f aca="false">$G$1</f>
-        <v>550</v>
+        <v>518</v>
       </c>
       <c r="D42" s="22" t="n">
         <f aca="false">(( -A42 - (-0.25) ) * SIN(RADIANS($F$1)) + (B42 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>38.4219465689307</v>
+        <v>36.1748385867384</v>
       </c>
       <c r="E42" s="22" t="n">
         <f aca="false">(( -A42 - (-0.25) ) * COS(RADIANS($F$1)) - (B42 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>0</v>
+        <v>-100.876660887038</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4024,15 +4063,15 @@
       </c>
       <c r="C43" s="20" t="n">
         <f aca="false">$G$1</f>
-        <v>550</v>
+        <v>518</v>
       </c>
       <c r="D43" s="20" t="n">
         <f aca="false">(( -A43 - (-0.25) ) * SIN(RADIANS($F$1)) + (B43 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>37.6767465689307</v>
+        <v>35.2433385867384</v>
       </c>
       <c r="E43" s="20" t="n">
         <f aca="false">(( -A43 - (-0.25) ) * COS(RADIANS($F$1)) - (B43 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-0.176400000000002</v>
+        <v>-101.097160887038</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4044,15 +4083,15 @@
       </c>
       <c r="C44" s="22" t="n">
         <f aca="false">$G$1</f>
-        <v>550</v>
+        <v>518</v>
       </c>
       <c r="D44" s="22" t="n">
         <f aca="false">(( -A44 - (-0.25) ) * SIN(RADIANS($F$1)) + (B44 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>37.0431465689307</v>
+        <v>34.4513385867384</v>
       </c>
       <c r="E44" s="22" t="n">
         <f aca="false">(( -A44 - (-0.25) ) * COS(RADIANS($F$1)) - (B44 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-0.986400000000002</v>
+        <v>-102.109660887038</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4064,15 +4103,15 @@
       </c>
       <c r="C45" s="20" t="n">
         <f aca="false">$G$1</f>
-        <v>550</v>
+        <v>518</v>
       </c>
       <c r="D45" s="20" t="n">
         <f aca="false">(( -A45 - (-0.25) ) * SIN(RADIANS($F$1)) + (B45 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>36.8919465689307</v>
+        <v>34.2623385867384</v>
       </c>
       <c r="E45" s="20" t="n">
         <f aca="false">(( -A45 - (-0.25) ) * COS(RADIANS($F$1)) - (B45 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-2.4084</v>
+        <v>-103.887160887038</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4084,15 +4123,15 @@
       </c>
       <c r="C46" s="22" t="n">
         <f aca="false">$G$1</f>
-        <v>550</v>
+        <v>518</v>
       </c>
       <c r="D46" s="22" t="n">
         <f aca="false">(( -A46 - (-0.25) ) * SIN(RADIANS($F$1)) + (B46 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>37.1025465689307</v>
+        <v>34.5255885867384</v>
       </c>
       <c r="E46" s="22" t="n">
         <f aca="false">(( -A46 - (-0.25) ) * COS(RADIANS($F$1)) - (B46 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-4.3794</v>
+        <v>-106.350910887038</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4104,15 +4143,15 @@
       </c>
       <c r="C47" s="20" t="n">
         <f aca="false">$G$1</f>
-        <v>550</v>
+        <v>518</v>
       </c>
       <c r="D47" s="20" t="n">
         <f aca="false">(( -A47 - (-0.25) ) * SIN(RADIANS($F$1)) + (B47 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>37.4895465689307</v>
+        <v>35.0093385867384</v>
       </c>
       <c r="E47" s="20" t="n">
         <f aca="false">(( -A47 - (-0.25) ) * COS(RADIANS($F$1)) - (B47 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-6.8598</v>
+        <v>-109.451410887038</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4124,15 +4163,15 @@
       </c>
       <c r="C48" s="22" t="n">
         <f aca="false">$G$1</f>
-        <v>550</v>
+        <v>518</v>
       </c>
       <c r="D48" s="22" t="n">
         <f aca="false">(( -A48 - (-0.25) ) * SIN(RADIANS($F$1)) + (B48 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>37.9341465689307</v>
+        <v>35.5650885867384</v>
       </c>
       <c r="E48" s="22" t="n">
         <f aca="false">(( -A48 - (-0.25) ) * COS(RADIANS($F$1)) - (B48 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-9.8424</v>
+        <v>-113.179660887038</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4144,15 +4183,15 @@
       </c>
       <c r="C49" s="20" t="n">
         <f aca="false">$G$1</f>
-        <v>550</v>
+        <v>518</v>
       </c>
       <c r="D49" s="20" t="n">
         <f aca="false">(( -A49 - (-0.25) ) * SIN(RADIANS($F$1)) + (B49 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>38.4201465689307</v>
+        <v>36.1725885867384</v>
       </c>
       <c r="E49" s="20" t="n">
         <f aca="false">(( -A49 - (-0.25) ) * COS(RADIANS($F$1)) - (B49 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-13.311</v>
+        <v>-117.515410887038</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4164,15 +4203,15 @@
       </c>
       <c r="C50" s="22" t="n">
         <f aca="false">$G$1</f>
-        <v>550</v>
+        <v>518</v>
       </c>
       <c r="D50" s="22" t="n">
         <f aca="false">(( -A50 - (-0.25) ) * SIN(RADIANS($F$1)) + (B50 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>38.9457465689307</v>
+        <v>36.8295885867384</v>
       </c>
       <c r="E50" s="22" t="n">
         <f aca="false">(( -A50 - (-0.25) ) * COS(RADIANS($F$1)) - (B50 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-17.2368</v>
+        <v>-122.422660887038</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4184,15 +4223,15 @@
       </c>
       <c r="C51" s="20" t="n">
         <f aca="false">$G$1</f>
-        <v>550</v>
+        <v>518</v>
       </c>
       <c r="D51" s="20" t="n">
         <f aca="false">(( -A51 - (-0.25) ) * SIN(RADIANS($F$1)) + (B51 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>39.5109465689307</v>
+        <v>37.5360885867384</v>
       </c>
       <c r="E51" s="20" t="n">
         <f aca="false">(( -A51 - (-0.25) ) * COS(RADIANS($F$1)) - (B51 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-21.5982</v>
+        <v>-127.874410887038</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4204,15 +4243,15 @@
       </c>
       <c r="C52" s="22" t="n">
         <f aca="false">$G$1</f>
-        <v>550</v>
+        <v>518</v>
       </c>
       <c r="D52" s="22" t="n">
         <f aca="false">(( -A52 - (-0.25) ) * SIN(RADIANS($F$1)) + (B52 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>40.1175465689307</v>
+        <v>38.2943385867384</v>
       </c>
       <c r="E52" s="22" t="n">
         <f aca="false">(( -A52 - (-0.25) ) * COS(RADIANS($F$1)) - (B52 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-26.3664</v>
+        <v>-133.834660887038</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4224,15 +4263,15 @@
       </c>
       <c r="C53" s="20" t="n">
         <f aca="false">$G$1</f>
-        <v>550</v>
+        <v>518</v>
       </c>
       <c r="D53" s="20" t="n">
         <f aca="false">(( -A53 - (-0.25) ) * SIN(RADIANS($F$1)) + (B53 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>40.7619465689307</v>
+        <v>39.0998385867384</v>
       </c>
       <c r="E53" s="20" t="n">
         <f aca="false">(( -A53 - (-0.25) ) * COS(RADIANS($F$1)) - (B53 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-31.5072</v>
+        <v>-140.260660887038</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4244,15 +4283,15 @@
       </c>
       <c r="C54" s="22" t="n">
         <f aca="false">$G$1</f>
-        <v>550</v>
+        <v>518</v>
       </c>
       <c r="D54" s="22" t="n">
         <f aca="false">(( -A54 - (-0.25) ) * SIN(RADIANS($F$1)) + (B54 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>41.4315465689307</v>
+        <v>39.9368385867384</v>
       </c>
       <c r="E54" s="22" t="n">
         <f aca="false">(( -A54 - (-0.25) ) * COS(RADIANS($F$1)) - (B54 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-36.9882</v>
+        <v>-147.111910887038</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4264,15 +4303,15 @@
       </c>
       <c r="C55" s="20" t="n">
         <f aca="false">$G$1</f>
-        <v>550</v>
+        <v>518</v>
       </c>
       <c r="D55" s="20" t="n">
         <f aca="false">(( -A55 - (-0.25) ) * SIN(RADIANS($F$1)) + (B55 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>42.1137465689307</v>
+        <v>40.7895885867384</v>
       </c>
       <c r="E55" s="20" t="n">
         <f aca="false">(( -A55 - (-0.25) ) * COS(RADIANS($F$1)) - (B55 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-42.768</v>
+        <v>-154.336660887038</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4284,15 +4323,15 @@
       </c>
       <c r="C56" s="22" t="n">
         <f aca="false">$G$1</f>
-        <v>550</v>
+        <v>518</v>
       </c>
       <c r="D56" s="22" t="n">
         <f aca="false">(( -A56 - (-0.25) ) * SIN(RADIANS($F$1)) + (B56 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>42.7977465689307</v>
+        <v>41.6445885867384</v>
       </c>
       <c r="E56" s="22" t="n">
         <f aca="false">(( -A56 - (-0.25) ) * COS(RADIANS($F$1)) - (B56 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-48.816</v>
+        <v>-161.896660887038</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4304,15 +4343,15 @@
       </c>
       <c r="C57" s="20" t="n">
         <f aca="false">$G$1</f>
-        <v>550</v>
+        <v>518</v>
       </c>
       <c r="D57" s="20" t="n">
         <f aca="false">(( -A57 - (-0.25) ) * SIN(RADIANS($F$1)) + (B57 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>43.4745465689307</v>
+        <v>42.4905885867384</v>
       </c>
       <c r="E57" s="20" t="n">
         <f aca="false">(( -A57 - (-0.25) ) * COS(RADIANS($F$1)) - (B57 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-55.0962</v>
+        <v>-169.746910887038</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4324,15 +4363,15 @@
       </c>
       <c r="C58" s="22" t="n">
         <f aca="false">$G$1</f>
-        <v>550</v>
+        <v>518</v>
       </c>
       <c r="D58" s="22" t="n">
         <f aca="false">(( -A58 - (-0.25) ) * SIN(RADIANS($F$1)) + (B58 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>44.1333465689307</v>
+        <v>43.3140885867384</v>
       </c>
       <c r="E58" s="22" t="n">
         <f aca="false">(( -A58 - (-0.25) ) * COS(RADIANS($F$1)) - (B58 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-61.5672</v>
+        <v>-177.835660887038</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4344,15 +4383,15 @@
       </c>
       <c r="C59" s="20" t="n">
         <f aca="false">$G$1</f>
-        <v>550</v>
+        <v>518</v>
       </c>
       <c r="D59" s="20" t="n">
         <f aca="false">(( -A59 - (-0.25) ) * SIN(RADIANS($F$1)) + (B59 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>44.7651465689307</v>
+        <v>44.1038385867384</v>
       </c>
       <c r="E59" s="20" t="n">
         <f aca="false">(( -A59 - (-0.25) ) * COS(RADIANS($F$1)) - (B59 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-68.1966</v>
+        <v>-186.122410887038</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4364,15 +4403,15 @@
       </c>
       <c r="C60" s="22" t="n">
         <f aca="false">$G$1</f>
-        <v>550</v>
+        <v>518</v>
       </c>
       <c r="D60" s="22" t="n">
         <f aca="false">(( -A60 - (-0.25) ) * SIN(RADIANS($F$1)) + (B60 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>45.3573465689307</v>
+        <v>44.8440885867384</v>
       </c>
       <c r="E60" s="22" t="n">
         <f aca="false">(( -A60 - (-0.25) ) * COS(RADIANS($F$1)) - (B60 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-74.9484</v>
+        <v>-194.562160887038</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4384,15 +4423,15 @@
       </c>
       <c r="C61" s="20" t="n">
         <f aca="false">$G$1</f>
-        <v>550</v>
+        <v>518</v>
       </c>
       <c r="D61" s="20" t="n">
         <f aca="false">(( -A61 - (-0.25) ) * SIN(RADIANS($F$1)) + (B61 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>45.9009465689307</v>
+        <v>45.5235885867384</v>
       </c>
       <c r="E61" s="20" t="n">
         <f aca="false">(( -A61 - (-0.25) ) * COS(RADIANS($F$1)) - (B61 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-81.783</v>
+        <v>-203.105410887038</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4404,15 +4443,15 @@
       </c>
       <c r="C62" s="22" t="n">
         <f aca="false">$G$1</f>
-        <v>550</v>
+        <v>518</v>
       </c>
       <c r="D62" s="22" t="n">
         <f aca="false">(( -A62 - (-0.25) ) * SIN(RADIANS($F$1)) + (B62 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>46.3797465689307</v>
+        <v>46.1220885867384</v>
       </c>
       <c r="E62" s="22" t="n">
         <f aca="false">(( -A62 - (-0.25) ) * COS(RADIANS($F$1)) - (B62 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-88.677</v>
+        <v>-211.722910887038</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4424,15 +4463,15 @@
       </c>
       <c r="C63" s="20" t="n">
         <f aca="false">$G$1</f>
-        <v>550</v>
+        <v>518</v>
       </c>
       <c r="D63" s="20" t="n">
         <f aca="false">(( -A63 - (-0.25) ) * SIN(RADIANS($F$1)) + (B63 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>46.7829465689307</v>
+        <v>46.6260885867384</v>
       </c>
       <c r="E63" s="20" t="n">
         <f aca="false">(( -A63 - (-0.25) ) * COS(RADIANS($F$1)) - (B63 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-95.5782</v>
+        <v>-220.349410887038</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4444,15 +4483,15 @@
       </c>
       <c r="C64" s="22" t="n">
         <f aca="false">$G$1</f>
-        <v>550</v>
+        <v>518</v>
       </c>
       <c r="D64" s="22" t="n">
         <f aca="false">(( -A64 - (-0.25) ) * SIN(RADIANS($F$1)) + (B64 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>47.1015465689307</v>
+        <v>47.0243385867384</v>
       </c>
       <c r="E64" s="22" t="n">
         <f aca="false">(( -A64 - (-0.25) ) * COS(RADIANS($F$1)) - (B64 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-102.4866</v>
+        <v>-228.984910887038</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4464,15 +4503,15 @@
       </c>
       <c r="C65" s="20" t="n">
         <f aca="false">$G$1</f>
-        <v>550</v>
+        <v>518</v>
       </c>
       <c r="D65" s="20" t="n">
         <f aca="false">(( -A65 - (-0.25) ) * SIN(RADIANS($F$1)) + (B65 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>47.3247465689307</v>
+        <v>47.3033385867384</v>
       </c>
       <c r="E65" s="20" t="n">
         <f aca="false">(( -A65 - (-0.25) ) * COS(RADIANS($F$1)) - (B65 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-109.4004</v>
+        <v>-237.627160887038</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4484,15 +4523,15 @@
       </c>
       <c r="C66" s="22" t="n">
         <f aca="false">$G$1</f>
-        <v>550</v>
+        <v>518</v>
       </c>
       <c r="D66" s="22" t="n">
         <f aca="false">(( -A66 - (-0.25) ) * SIN(RADIANS($F$1)) + (B66 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>47.4453465689307</v>
+        <v>47.4540885867384</v>
       </c>
       <c r="E66" s="22" t="n">
         <f aca="false">(( -A66 - (-0.25) ) * COS(RADIANS($F$1)) - (B66 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-116.2692</v>
+        <v>-246.213160887038</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4504,15 +4543,15 @@
       </c>
       <c r="C67" s="20" t="n">
         <f aca="false">$G$1</f>
-        <v>550</v>
+        <v>518</v>
       </c>
       <c r="D67" s="20" t="n">
         <f aca="false">(( -A67 - (-0.25) ) * SIN(RADIANS($F$1)) + (B67 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>47.4543465689307</v>
+        <v>47.4653385867384</v>
       </c>
       <c r="E67" s="20" t="n">
         <f aca="false">(( -A67 - (-0.25) ) * COS(RADIANS($F$1)) - (B67 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-123.0462</v>
+        <v>-254.684410887038</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4524,15 +4563,15 @@
       </c>
       <c r="C68" s="22" t="n">
         <f aca="false">$G$1</f>
-        <v>550</v>
+        <v>518</v>
       </c>
       <c r="D68" s="22" t="n">
         <f aca="false">(( -A68 - (-0.25) ) * SIN(RADIANS($F$1)) + (B68 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>47.3445465689307</v>
+        <v>47.3280885867384</v>
       </c>
       <c r="E68" s="22" t="n">
         <f aca="false">(( -A68 - (-0.25) ) * COS(RADIANS($F$1)) - (B68 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-129.6774</v>
+        <v>-262.973410887038</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4544,15 +4583,15 @@
       </c>
       <c r="C69" s="20" t="n">
         <f aca="false">$G$1</f>
-        <v>550</v>
+        <v>518</v>
       </c>
       <c r="D69" s="20" t="n">
         <f aca="false">(( -A69 - (-0.25) ) * SIN(RADIANS($F$1)) + (B69 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>47.1123465689307</v>
+        <v>47.0378385867384</v>
       </c>
       <c r="E69" s="20" t="n">
         <f aca="false">(( -A69 - (-0.25) ) * COS(RADIANS($F$1)) - (B69 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-136.1088</v>
+        <v>-271.012660887038</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4564,15 +4603,15 @@
       </c>
       <c r="C70" s="22" t="n">
         <f aca="false">$G$1</f>
-        <v>550</v>
+        <v>518</v>
       </c>
       <c r="D70" s="22" t="n">
         <f aca="false">(( -A70 - (-0.25) ) * SIN(RADIANS($F$1)) + (B70 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>46.7541465689307</v>
+        <v>46.5900885867384</v>
       </c>
       <c r="E70" s="22" t="n">
         <f aca="false">(( -A70 - (-0.25) ) * COS(RADIANS($F$1)) - (B70 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-142.2864</v>
+        <v>-278.734660887038</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4584,15 +4623,15 @@
       </c>
       <c r="C71" s="20" t="n">
         <f aca="false">$G$1</f>
-        <v>550</v>
+        <v>518</v>
       </c>
       <c r="D71" s="20" t="n">
         <f aca="false">(( -A71 - (-0.25) ) * SIN(RADIANS($F$1)) + (B71 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>46.2609465689307</v>
+        <v>45.9735885867384</v>
       </c>
       <c r="E71" s="20" t="n">
         <f aca="false">(( -A71 - (-0.25) ) * COS(RADIANS($F$1)) - (B71 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-148.1562</v>
+        <v>-286.071910887038</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4604,15 +4643,15 @@
       </c>
       <c r="C72" s="22" t="n">
         <f aca="false">$G$1</f>
-        <v>550</v>
+        <v>518</v>
       </c>
       <c r="D72" s="22" t="n">
         <f aca="false">(( -A72 - (-0.25) ) * SIN(RADIANS($F$1)) + (B72 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>45.6201465689307</v>
+        <v>45.1725885867384</v>
       </c>
       <c r="E72" s="22" t="n">
         <f aca="false">(( -A72 - (-0.25) ) * COS(RADIANS($F$1)) - (B72 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-153.666</v>
+        <v>-292.959160887038</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4624,15 +4663,15 @@
       </c>
       <c r="C73" s="20" t="n">
         <f aca="false">$G$1</f>
-        <v>550</v>
+        <v>518</v>
       </c>
       <c r="D73" s="20" t="n">
         <f aca="false">(( -A73 - (-0.25) ) * SIN(RADIANS($F$1)) + (B73 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>44.8263465689307</v>
+        <v>44.1803385867384</v>
       </c>
       <c r="E73" s="20" t="n">
         <f aca="false">(( -A73 - (-0.25) ) * COS(RADIANS($F$1)) - (B73 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-158.7636</v>
+        <v>-299.331160887038</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4644,15 +4683,15 @@
       </c>
       <c r="C74" s="22" t="n">
         <f aca="false">$G$1</f>
-        <v>550</v>
+        <v>518</v>
       </c>
       <c r="D74" s="22" t="n">
         <f aca="false">(( -A74 - (-0.25) ) * SIN(RADIANS($F$1)) + (B74 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>43.8831465689307</v>
+        <v>43.0013385867384</v>
       </c>
       <c r="E74" s="22" t="n">
         <f aca="false">(( -A74 - (-0.25) ) * COS(RADIANS($F$1)) - (B74 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-163.395</v>
+        <v>-305.120410887038</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4664,15 +4703,15 @@
       </c>
       <c r="C75" s="20" t="n">
         <f aca="false">$G$1</f>
-        <v>550</v>
+        <v>518</v>
       </c>
       <c r="D75" s="20" t="n">
         <f aca="false">(( -A75 - (-0.25) ) * SIN(RADIANS($F$1)) + (B75 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>42.8409465689307</v>
+        <v>41.6985885867384</v>
       </c>
       <c r="E75" s="20" t="n">
         <f aca="false">(( -A75 - (-0.25) ) * COS(RADIANS($F$1)) - (B75 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-167.5152</v>
+        <v>-310.270660887038</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4684,15 +4723,15 @@
       </c>
       <c r="C76" s="22" t="n">
         <f aca="false">$G$1</f>
-        <v>550</v>
+        <v>518</v>
       </c>
       <c r="D76" s="22" t="n">
         <f aca="false">(( -A76 - (-0.25) ) * SIN(RADIANS($F$1)) + (B76 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>41.7915465689307</v>
+        <v>40.3868385867384</v>
       </c>
       <c r="E76" s="22" t="n">
         <f aca="false">(( -A76 - (-0.25) ) * COS(RADIANS($F$1)) - (B76 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-171.0792</v>
+        <v>-314.725660887038</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4704,15 +4743,15 @@
       </c>
       <c r="C77" s="20" t="n">
         <f aca="false">$G$1</f>
-        <v>550</v>
+        <v>518</v>
       </c>
       <c r="D77" s="20" t="n">
         <f aca="false">(( -A77 - (-0.25) ) * SIN(RADIANS($F$1)) + (B77 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>40.7817465689307</v>
+        <v>39.1245885867384</v>
       </c>
       <c r="E77" s="20" t="n">
         <f aca="false">(( -A77 - (-0.25) ) * COS(RADIANS($F$1)) - (B77 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-174.0564</v>
+        <v>-318.447160887038</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4724,15 +4763,15 @@
       </c>
       <c r="C78" s="22" t="n">
         <f aca="false">$G$1</f>
-        <v>550</v>
+        <v>518</v>
       </c>
       <c r="D78" s="22" t="n">
         <f aca="false">(( -A78 - (-0.25) ) * SIN(RADIANS($F$1)) + (B78 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>39.8205465689307</v>
+        <v>37.9230885867384</v>
       </c>
       <c r="E78" s="22" t="n">
         <f aca="false">(( -A78 - (-0.25) ) * COS(RADIANS($F$1)) - (B78 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-176.4666</v>
+        <v>-321.459910887038</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4744,15 +4783,15 @@
       </c>
       <c r="C79" s="20" t="n">
         <f aca="false">$G$1</f>
-        <v>550</v>
+        <v>518</v>
       </c>
       <c r="D79" s="20" t="n">
         <f aca="false">(( -A79 - (-0.25) ) * SIN(RADIANS($F$1)) + (B79 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>39.0339465689307</v>
+        <v>36.9398385867384</v>
       </c>
       <c r="E79" s="20" t="n">
         <f aca="false">(( -A79 - (-0.25) ) * COS(RADIANS($F$1)) - (B79 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-178.326</v>
+        <v>-323.784160887038</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4764,15 +4803,15 @@
       </c>
       <c r="C80" s="22" t="n">
         <f aca="false">$G$1</f>
-        <v>550</v>
+        <v>518</v>
       </c>
       <c r="D80" s="22" t="n">
         <f aca="false">(( -A80 - (-0.25) ) * SIN(RADIANS($F$1)) + (B80 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>38.5821465689307</v>
+        <v>36.3750885867384</v>
       </c>
       <c r="E80" s="22" t="n">
         <f aca="false">(( -A80 - (-0.25) ) * COS(RADIANS($F$1)) - (B80 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-179.5572</v>
+        <v>-325.323160887038</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4784,15 +4823,15 @@
       </c>
       <c r="C81" s="20" t="n">
         <f aca="false">$G$1</f>
-        <v>550</v>
+        <v>518</v>
       </c>
       <c r="D81" s="20" t="n">
         <f aca="false">(( -A81 - (-0.25) ) * SIN(RADIANS($F$1)) + (B81 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>38.4597465689307</v>
+        <v>36.2220885867384</v>
       </c>
       <c r="E81" s="20" t="n">
         <f aca="false">(( -A81 - (-0.25) ) * COS(RADIANS($F$1)) - (B81 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-180</v>
+        <v>-325.876660887038</v>
       </c>
     </row>
   </sheetData>

--- a/AIRCRAFT_AIRFOIL_TRANSFORM_MICRO26.xlsx
+++ b/AIRCRAFT_AIRFOIL_TRANSFORM_MICRO26.xlsx
@@ -1121,7 +1121,7 @@
         <v>31</v>
       </c>
       <c r="C10" s="8" t="n">
-        <v>11.02</v>
+        <v>12.2004687</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>23</v>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H1" s="17" t="n">
         <f aca="false">Control_Panel!$C$10</f>
-        <v>11.02</v>
+        <v>12.2004687</v>
       </c>
       <c r="I1" s="17" t="n">
         <f aca="false">Control_Panel!$C$11</f>
@@ -3218,7 +3218,7 @@
       </c>
       <c r="H1" s="17" t="n">
         <f aca="false">Control_Panel!$C$10</f>
-        <v>11.02</v>
+        <v>12.2004687</v>
       </c>
       <c r="I1" s="17" t="n">
         <f aca="false">Control_Panel!$C$11</f>
@@ -3271,7 +3271,7 @@
       </c>
       <c r="E3" s="20" t="n">
         <f aca="false">(( -A3 - (-0.25) ) * COS(RADIANS($F$1)) - (B3 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-325.876660887038</v>
+        <v>-336.999999740883</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3291,7 +3291,7 @@
       </c>
       <c r="E4" s="22" t="n">
         <f aca="false">(( -A4 - (-0.25) ) * COS(RADIANS($F$1)) - (B4 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-325.323160887038</v>
+        <v>-336.446499740883</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3311,7 +3311,7 @@
       </c>
       <c r="E5" s="20" t="n">
         <f aca="false">(( -A5 - (-0.25) ) * COS(RADIANS($F$1)) - (B5 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-323.784160887038</v>
+        <v>-334.907499740883</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="E6" s="22" t="n">
         <f aca="false">(( -A6 - (-0.25) ) * COS(RADIANS($F$1)) - (B6 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-321.459910887038</v>
+        <v>-332.583249740883</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3351,7 +3351,7 @@
       </c>
       <c r="E7" s="20" t="n">
         <f aca="false">(( -A7 - (-0.25) ) * COS(RADIANS($F$1)) - (B7 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-318.447160887038</v>
+        <v>-329.570499740883</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3371,7 +3371,7 @@
       </c>
       <c r="E8" s="22" t="n">
         <f aca="false">(( -A8 - (-0.25) ) * COS(RADIANS($F$1)) - (B8 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-314.725660887038</v>
+        <v>-325.848999740883</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E9" s="20" t="n">
         <f aca="false">(( -A9 - (-0.25) ) * COS(RADIANS($F$1)) - (B9 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-310.270660887038</v>
+        <v>-321.393999740883</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3411,7 +3411,7 @@
       </c>
       <c r="E10" s="22" t="n">
         <f aca="false">(( -A10 - (-0.25) ) * COS(RADIANS($F$1)) - (B10 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-305.120410887038</v>
+        <v>-316.243749740883</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3431,7 +3431,7 @@
       </c>
       <c r="E11" s="20" t="n">
         <f aca="false">(( -A11 - (-0.25) ) * COS(RADIANS($F$1)) - (B11 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-299.331160887038</v>
+        <v>-310.454499740883</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3451,7 +3451,7 @@
       </c>
       <c r="E12" s="22" t="n">
         <f aca="false">(( -A12 - (-0.25) ) * COS(RADIANS($F$1)) - (B12 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-292.959160887038</v>
+        <v>-304.082499740883</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="E13" s="20" t="n">
         <f aca="false">(( -A13 - (-0.25) ) * COS(RADIANS($F$1)) - (B13 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-286.071910887038</v>
+        <v>-297.195249740883</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="E14" s="22" t="n">
         <f aca="false">(( -A14 - (-0.25) ) * COS(RADIANS($F$1)) - (B14 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-278.734660887038</v>
+        <v>-289.857999740883</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="E15" s="20" t="n">
         <f aca="false">(( -A15 - (-0.25) ) * COS(RADIANS($F$1)) - (B15 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-271.012660887038</v>
+        <v>-282.135999740883</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E16" s="22" t="n">
         <f aca="false">(( -A16 - (-0.25) ) * COS(RADIANS($F$1)) - (B16 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-262.973410887038</v>
+        <v>-274.096749740883</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3551,7 +3551,7 @@
       </c>
       <c r="E17" s="20" t="n">
         <f aca="false">(( -A17 - (-0.25) ) * COS(RADIANS($F$1)) - (B17 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-254.684410887038</v>
+        <v>-265.807749740883</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3571,7 +3571,7 @@
       </c>
       <c r="E18" s="22" t="n">
         <f aca="false">(( -A18 - (-0.25) ) * COS(RADIANS($F$1)) - (B18 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-246.213160887038</v>
+        <v>-257.336499740883</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3591,7 +3591,7 @@
       </c>
       <c r="E19" s="20" t="n">
         <f aca="false">(( -A19 - (-0.25) ) * COS(RADIANS($F$1)) - (B19 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-237.627160887038</v>
+        <v>-248.750499740883</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="E20" s="22" t="n">
         <f aca="false">(( -A20 - (-0.25) ) * COS(RADIANS($F$1)) - (B20 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-228.984910887038</v>
+        <v>-240.108249740883</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3631,7 +3631,7 @@
       </c>
       <c r="E21" s="20" t="n">
         <f aca="false">(( -A21 - (-0.25) ) * COS(RADIANS($F$1)) - (B21 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-220.349410887038</v>
+        <v>-231.472749740883</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3651,7 +3651,7 @@
       </c>
       <c r="E22" s="22" t="n">
         <f aca="false">(( -A22 - (-0.25) ) * COS(RADIANS($F$1)) - (B22 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-211.722910887038</v>
+        <v>-222.846249740883</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E23" s="20" t="n">
         <f aca="false">(( -A23 - (-0.25) ) * COS(RADIANS($F$1)) - (B23 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-203.105410887038</v>
+        <v>-214.228749740883</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3691,7 +3691,7 @@
       </c>
       <c r="E24" s="22" t="n">
         <f aca="false">(( -A24 - (-0.25) ) * COS(RADIANS($F$1)) - (B24 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-194.562160887038</v>
+        <v>-205.685499740883</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3711,7 +3711,7 @@
       </c>
       <c r="E25" s="20" t="n">
         <f aca="false">(( -A25 - (-0.25) ) * COS(RADIANS($F$1)) - (B25 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-186.122410887038</v>
+        <v>-197.245749740883</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3731,7 +3731,7 @@
       </c>
       <c r="E26" s="22" t="n">
         <f aca="false">(( -A26 - (-0.25) ) * COS(RADIANS($F$1)) - (B26 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-177.835660887038</v>
+        <v>-188.958999740883</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="E27" s="20" t="n">
         <f aca="false">(( -A27 - (-0.25) ) * COS(RADIANS($F$1)) - (B27 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-169.746910887038</v>
+        <v>-180.870249740883</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3771,7 +3771,7 @@
       </c>
       <c r="E28" s="22" t="n">
         <f aca="false">(( -A28 - (-0.25) ) * COS(RADIANS($F$1)) - (B28 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-161.896660887038</v>
+        <v>-173.019999740883</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3791,7 +3791,7 @@
       </c>
       <c r="E29" s="20" t="n">
         <f aca="false">(( -A29 - (-0.25) ) * COS(RADIANS($F$1)) - (B29 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-154.336660887038</v>
+        <v>-165.459999740883</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E30" s="22" t="n">
         <f aca="false">(( -A30 - (-0.25) ) * COS(RADIANS($F$1)) - (B30 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-147.111910887038</v>
+        <v>-158.235249740883</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3831,7 +3831,7 @@
       </c>
       <c r="E31" s="20" t="n">
         <f aca="false">(( -A31 - (-0.25) ) * COS(RADIANS($F$1)) - (B31 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-140.260660887038</v>
+        <v>-151.383999740883</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3851,7 +3851,7 @@
       </c>
       <c r="E32" s="22" t="n">
         <f aca="false">(( -A32 - (-0.25) ) * COS(RADIANS($F$1)) - (B32 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-133.834660887038</v>
+        <v>-144.957999740883</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3871,7 +3871,7 @@
       </c>
       <c r="E33" s="20" t="n">
         <f aca="false">(( -A33 - (-0.25) ) * COS(RADIANS($F$1)) - (B33 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-127.874410887038</v>
+        <v>-138.997749740883</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="E34" s="22" t="n">
         <f aca="false">(( -A34 - (-0.25) ) * COS(RADIANS($F$1)) - (B34 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-122.422660887038</v>
+        <v>-133.545999740883</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3911,7 +3911,7 @@
       </c>
       <c r="E35" s="20" t="n">
         <f aca="false">(( -A35 - (-0.25) ) * COS(RADIANS($F$1)) - (B35 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-117.515410887038</v>
+        <v>-128.638749740883</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3931,7 +3931,7 @@
       </c>
       <c r="E36" s="22" t="n">
         <f aca="false">(( -A36 - (-0.25) ) * COS(RADIANS($F$1)) - (B36 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-113.179660887038</v>
+        <v>-124.302999740883</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E37" s="20" t="n">
         <f aca="false">(( -A37 - (-0.25) ) * COS(RADIANS($F$1)) - (B37 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-109.451410887038</v>
+        <v>-120.574749740883</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3971,7 +3971,7 @@
       </c>
       <c r="E38" s="22" t="n">
         <f aca="false">(( -A38 - (-0.25) ) * COS(RADIANS($F$1)) - (B38 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-106.350910887038</v>
+        <v>-117.474249740883</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3991,7 +3991,7 @@
       </c>
       <c r="E39" s="20" t="n">
         <f aca="false">(( -A39 - (-0.25) ) * COS(RADIANS($F$1)) - (B39 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-103.887160887038</v>
+        <v>-115.010499740883</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4011,7 +4011,7 @@
       </c>
       <c r="E40" s="22" t="n">
         <f aca="false">(( -A40 - (-0.25) ) * COS(RADIANS($F$1)) - (B40 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-102.109660887038</v>
+        <v>-113.232999740883</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="E41" s="20" t="n">
         <f aca="false">(( -A41 - (-0.25) ) * COS(RADIANS($F$1)) - (B41 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-101.097160887038</v>
+        <v>-112.220499740883</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4051,7 +4051,7 @@
       </c>
       <c r="E42" s="22" t="n">
         <f aca="false">(( -A42 - (-0.25) ) * COS(RADIANS($F$1)) - (B42 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-100.876660887038</v>
+        <v>-111.999999740883</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4071,7 +4071,7 @@
       </c>
       <c r="E43" s="20" t="n">
         <f aca="false">(( -A43 - (-0.25) ) * COS(RADIANS($F$1)) - (B43 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-101.097160887038</v>
+        <v>-112.220499740883</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E44" s="22" t="n">
         <f aca="false">(( -A44 - (-0.25) ) * COS(RADIANS($F$1)) - (B44 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-102.109660887038</v>
+        <v>-113.232999740883</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4111,7 +4111,7 @@
       </c>
       <c r="E45" s="20" t="n">
         <f aca="false">(( -A45 - (-0.25) ) * COS(RADIANS($F$1)) - (B45 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-103.887160887038</v>
+        <v>-115.010499740883</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4131,7 +4131,7 @@
       </c>
       <c r="E46" s="22" t="n">
         <f aca="false">(( -A46 - (-0.25) ) * COS(RADIANS($F$1)) - (B46 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-106.350910887038</v>
+        <v>-117.474249740883</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4151,7 +4151,7 @@
       </c>
       <c r="E47" s="20" t="n">
         <f aca="false">(( -A47 - (-0.25) ) * COS(RADIANS($F$1)) - (B47 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-109.451410887038</v>
+        <v>-120.574749740883</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="E48" s="22" t="n">
         <f aca="false">(( -A48 - (-0.25) ) * COS(RADIANS($F$1)) - (B48 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-113.179660887038</v>
+        <v>-124.302999740883</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="E49" s="20" t="n">
         <f aca="false">(( -A49 - (-0.25) ) * COS(RADIANS($F$1)) - (B49 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-117.515410887038</v>
+        <v>-128.638749740883</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="E50" s="22" t="n">
         <f aca="false">(( -A50 - (-0.25) ) * COS(RADIANS($F$1)) - (B50 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-122.422660887038</v>
+        <v>-133.545999740883</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E51" s="20" t="n">
         <f aca="false">(( -A51 - (-0.25) ) * COS(RADIANS($F$1)) - (B51 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-127.874410887038</v>
+        <v>-138.997749740883</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4251,7 +4251,7 @@
       </c>
       <c r="E52" s="22" t="n">
         <f aca="false">(( -A52 - (-0.25) ) * COS(RADIANS($F$1)) - (B52 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-133.834660887038</v>
+        <v>-144.957999740883</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4271,7 +4271,7 @@
       </c>
       <c r="E53" s="20" t="n">
         <f aca="false">(( -A53 - (-0.25) ) * COS(RADIANS($F$1)) - (B53 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-140.260660887038</v>
+        <v>-151.383999740883</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4291,7 +4291,7 @@
       </c>
       <c r="E54" s="22" t="n">
         <f aca="false">(( -A54 - (-0.25) ) * COS(RADIANS($F$1)) - (B54 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-147.111910887038</v>
+        <v>-158.235249740883</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="E55" s="20" t="n">
         <f aca="false">(( -A55 - (-0.25) ) * COS(RADIANS($F$1)) - (B55 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-154.336660887038</v>
+        <v>-165.459999740883</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4331,7 +4331,7 @@
       </c>
       <c r="E56" s="22" t="n">
         <f aca="false">(( -A56 - (-0.25) ) * COS(RADIANS($F$1)) - (B56 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-161.896660887038</v>
+        <v>-173.019999740883</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4351,7 +4351,7 @@
       </c>
       <c r="E57" s="20" t="n">
         <f aca="false">(( -A57 - (-0.25) ) * COS(RADIANS($F$1)) - (B57 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-169.746910887038</v>
+        <v>-180.870249740883</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E58" s="22" t="n">
         <f aca="false">(( -A58 - (-0.25) ) * COS(RADIANS($F$1)) - (B58 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-177.835660887038</v>
+        <v>-188.958999740883</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4391,7 +4391,7 @@
       </c>
       <c r="E59" s="20" t="n">
         <f aca="false">(( -A59 - (-0.25) ) * COS(RADIANS($F$1)) - (B59 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-186.122410887038</v>
+        <v>-197.245749740883</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4411,7 +4411,7 @@
       </c>
       <c r="E60" s="22" t="n">
         <f aca="false">(( -A60 - (-0.25) ) * COS(RADIANS($F$1)) - (B60 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-194.562160887038</v>
+        <v>-205.685499740883</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="E61" s="20" t="n">
         <f aca="false">(( -A61 - (-0.25) ) * COS(RADIANS($F$1)) - (B61 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-203.105410887038</v>
+        <v>-214.228749740883</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="E62" s="22" t="n">
         <f aca="false">(( -A62 - (-0.25) ) * COS(RADIANS($F$1)) - (B62 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-211.722910887038</v>
+        <v>-222.846249740883</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="E63" s="20" t="n">
         <f aca="false">(( -A63 - (-0.25) ) * COS(RADIANS($F$1)) - (B63 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-220.349410887038</v>
+        <v>-231.472749740883</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4491,7 +4491,7 @@
       </c>
       <c r="E64" s="22" t="n">
         <f aca="false">(( -A64 - (-0.25) ) * COS(RADIANS($F$1)) - (B64 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-228.984910887038</v>
+        <v>-240.108249740883</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E65" s="20" t="n">
         <f aca="false">(( -A65 - (-0.25) ) * COS(RADIANS($F$1)) - (B65 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-237.627160887038</v>
+        <v>-248.750499740883</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4531,7 +4531,7 @@
       </c>
       <c r="E66" s="22" t="n">
         <f aca="false">(( -A66 - (-0.25) ) * COS(RADIANS($F$1)) - (B66 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-246.213160887038</v>
+        <v>-257.336499740883</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4551,7 +4551,7 @@
       </c>
       <c r="E67" s="20" t="n">
         <f aca="false">(( -A67 - (-0.25) ) * COS(RADIANS($F$1)) - (B67 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-254.684410887038</v>
+        <v>-265.807749740883</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4571,7 +4571,7 @@
       </c>
       <c r="E68" s="22" t="n">
         <f aca="false">(( -A68 - (-0.25) ) * COS(RADIANS($F$1)) - (B68 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-262.973410887038</v>
+        <v>-274.096749740883</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="E69" s="20" t="n">
         <f aca="false">(( -A69 - (-0.25) ) * COS(RADIANS($F$1)) - (B69 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-271.012660887038</v>
+        <v>-282.135999740883</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4611,7 +4611,7 @@
       </c>
       <c r="E70" s="22" t="n">
         <f aca="false">(( -A70 - (-0.25) ) * COS(RADIANS($F$1)) - (B70 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-278.734660887038</v>
+        <v>-289.857999740883</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4631,7 +4631,7 @@
       </c>
       <c r="E71" s="20" t="n">
         <f aca="false">(( -A71 - (-0.25) ) * COS(RADIANS($F$1)) - (B71 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-286.071910887038</v>
+        <v>-297.195249740883</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="E72" s="22" t="n">
         <f aca="false">(( -A72 - (-0.25) ) * COS(RADIANS($F$1)) - (B72 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-292.959160887038</v>
+        <v>-304.082499740883</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4671,7 +4671,7 @@
       </c>
       <c r="E73" s="20" t="n">
         <f aca="false">(( -A73 - (-0.25) ) * COS(RADIANS($F$1)) - (B73 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-299.331160887038</v>
+        <v>-310.454499740883</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4691,7 +4691,7 @@
       </c>
       <c r="E74" s="22" t="n">
         <f aca="false">(( -A74 - (-0.25) ) * COS(RADIANS($F$1)) - (B74 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-305.120410887038</v>
+        <v>-316.243749740883</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4711,7 +4711,7 @@
       </c>
       <c r="E75" s="20" t="n">
         <f aca="false">(( -A75 - (-0.25) ) * COS(RADIANS($F$1)) - (B75 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-310.270660887038</v>
+        <v>-321.393999740883</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="E76" s="22" t="n">
         <f aca="false">(( -A76 - (-0.25) ) * COS(RADIANS($F$1)) - (B76 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-314.725660887038</v>
+        <v>-325.848999740883</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4751,7 +4751,7 @@
       </c>
       <c r="E77" s="20" t="n">
         <f aca="false">(( -A77 - (-0.25) ) * COS(RADIANS($F$1)) - (B77 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-318.447160887038</v>
+        <v>-329.570499740883</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4771,7 +4771,7 @@
       </c>
       <c r="E78" s="22" t="n">
         <f aca="false">(( -A78 - (-0.25) ) * COS(RADIANS($F$1)) - (B78 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-321.459910887038</v>
+        <v>-332.583249740883</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="E79" s="20" t="n">
         <f aca="false">(( -A79 - (-0.25) ) * COS(RADIANS($F$1)) - (B79 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-323.784160887038</v>
+        <v>-334.907499740883</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4811,7 +4811,7 @@
       </c>
       <c r="E80" s="22" t="n">
         <f aca="false">(( -A80 - (-0.25) ) * COS(RADIANS($F$1)) - (B80 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-325.323160887038</v>
+        <v>-336.446499740883</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4831,7 +4831,7 @@
       </c>
       <c r="E81" s="20" t="n">
         <f aca="false">(( -A81 - (-0.25) ) * COS(RADIANS($F$1)) - (B81 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
-        <v>-325.876660887038</v>
+        <v>-336.999999740883</v>
       </c>
     </row>
   </sheetData>

--- a/AIRCRAFT_AIRFOIL_TRANSFORM_MICRO26.xlsx
+++ b/AIRCRAFT_AIRFOIL_TRANSFORM_MICRO26.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Calc"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
+  <fileVersion appName="Calc" lowestEdited="4"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
@@ -790,34 +790,34 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1f497d"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="eeece1"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4f81bd"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="c0504d"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9bbb59"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064a2"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4bacc6"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="f79646"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ff"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
         <a:srgbClr val="800080"/>
@@ -963,7 +963,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F30"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="30"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="20"/>
@@ -1508,7 +1508,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:I81"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="20"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="14"/>
@@ -2367,7 +2367,7 @@
         <v>0</v>
       </c>
       <c r="B42" s="21" t="n">
-        <v>-0.00021</v>
+        <v>0</v>
       </c>
       <c r="C42" s="22" t="n">
         <f aca="false">$G$1</f>
@@ -2375,7 +2375,7 @@
       </c>
       <c r="D42" s="22" t="n">
         <f aca="false">(( -A42 - (-0.25) ) * SIN(RADIANS($F$1)) + (B42 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>-0.04725</v>
+        <v>0</v>
       </c>
       <c r="E42" s="22" t="n">
         <f aca="false">(( -A42 - (-0.25) ) * COS(RADIANS($F$1)) - (B42 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
@@ -3179,7 +3179,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:I81"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="20"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="14"/>
@@ -4039,7 +4039,7 @@
         <v>0</v>
       </c>
       <c r="B42" s="21" t="n">
-        <v>-0.00021</v>
+        <v>0</v>
       </c>
       <c r="C42" s="22" t="n">
         <f aca="false">$G$1</f>
@@ -4047,7 +4047,7 @@
       </c>
       <c r="D42" s="22" t="n">
         <f aca="false">(( -A42 - (-0.25) ) * SIN(RADIANS($F$1)) + (B42 - 0) * COS(RADIANS($F$1)) - 0.25 * SIN(RADIANS($F$1))) * $E$1 + ($G$1 * TAN(RADIANS($I$1)))</f>
-        <v>36.1748385867384</v>
+        <v>36.2220885867384</v>
       </c>
       <c r="E42" s="22" t="n">
         <f aca="false">(( -A42 - (-0.25) ) * COS(RADIANS($F$1)) - (B42 - 0) * SIN(RADIANS($F$1)) + (-0.25)) * $E$1 - ($G$1 * TAN(RADIANS($H$1)))</f>
